--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FA6265-56F5-451C-A10F-7B282D1E9BCC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487B94DF-EB34-4E28-9858-DF460106FB38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1091,10 +1091,6 @@
     <t xml:space="preserve">130438120 ООО "НОВОЕ ВРЕМЯ"  93 Донецк г      Чаадаева ул.д.1        </t>
   </si>
   <si>
-    <t xml:space="preserve">130439104 ООО "НОВОЕ ВРЕМЯ"  Мариуполь (Бердянский р-н 90  Трояны)   
-</t>
-  </si>
-  <si>
     <t>Ротация кода 6353</t>
   </si>
   <si>
@@ -1198,6 +1194,10 @@
   </si>
   <si>
     <t>КОНСЕРВЫ МЯС.СВИНИНА ТУШ. В/С 325г_ЧЗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130439104 ООО "НОВОЕ ВРЕМЯ"  Мариуполь
+</t>
   </si>
 </sst>
 </file>
@@ -5563,7 +5563,7 @@
         <v>130439104</v>
       </c>
       <c r="L4" s="99" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.25">
@@ -5576,10 +5576,8 @@
       <c r="G5" s="8"/>
       <c r="H5" s="22"/>
       <c r="I5" s="22"/>
-      <c r="K5" s="27" t="str">
-        <f t="shared" ref="K5:K7" si="0">LEFT(L5,9)</f>
-        <v/>
-      </c>
+      <c r="K5" s="104"/>
+      <c r="L5" s="102"/>
     </row>
     <row r="6" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="39" t="s">
@@ -5591,7 +5589,7 @@
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
       <c r="K6" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K5:K7" si="0">LEFT(L6,9)</f>
         <v/>
       </c>
     </row>
@@ -6651,7 +6649,7 @@
         <v>7632</v>
       </c>
       <c r="B25" s="53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C25" s="50" t="s">
         <v>21</v>
@@ -6674,7 +6672,7 @@
         <v>60</v>
       </c>
       <c r="J25" s="52" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L25" s="102"/>
     </row>
@@ -6746,7 +6744,7 @@
         <v>8014</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C28" s="50" t="s">
         <v>23</v>
@@ -6833,7 +6831,7 @@
         <v>7514</v>
       </c>
       <c r="B29" s="53" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C29" s="50" t="s">
         <v>23</v>
@@ -6914,7 +6912,7 @@
         <v>7518</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C30" s="50" t="s">
         <v>23</v>
@@ -7447,7 +7445,7 @@
         <v>7461</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C37" s="50" t="s">
         <v>21</v>
@@ -7470,7 +7468,7 @@
         <v>30</v>
       </c>
       <c r="J37" s="52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K37" s="27"/>
       <c r="L37" s="102"/>
@@ -7536,7 +7534,7 @@
         <v>7040</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C38" s="50" t="s">
         <v>21</v>
@@ -7555,7 +7553,7 @@
       <c r="H38" s="29"/>
       <c r="I38" s="29"/>
       <c r="J38" s="105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K38" s="27"/>
       <c r="L38" s="102"/>
@@ -9627,7 +9625,7 @@
         <v>6946</v>
       </c>
       <c r="B81" s="53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C81" s="50" t="s">
         <v>23</v>
@@ -9745,7 +9743,7 @@
         <v>7562</v>
       </c>
       <c r="B85" s="53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C85" s="50" t="s">
         <v>23</v>
@@ -9801,7 +9799,7 @@
         <v>7489</v>
       </c>
       <c r="B87" s="53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C87" s="50" t="s">
         <v>21</v>
@@ -9820,7 +9818,7 @@
       <c r="H87" s="14"/>
       <c r="I87" s="14"/>
       <c r="J87" s="105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L87" s="102"/>
     </row>
@@ -9979,7 +9977,7 @@
         <v>7156</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C91" s="50" t="s">
         <v>21</v>
@@ -10155,7 +10153,7 @@
         <v>7516</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C95" s="50" t="s">
         <v>21</v>
@@ -10182,7 +10180,7 @@
         <v>7710</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C96" s="50" t="s">
         <v>21</v>
@@ -10209,7 +10207,7 @@
         <v>7513</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>21</v>
@@ -10329,7 +10327,7 @@
         <v>7608</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>21</v>
@@ -10352,7 +10350,7 @@
         <v>45</v>
       </c>
       <c r="J101" s="52" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L101" s="102"/>
     </row>
@@ -10362,7 +10360,7 @@
         <v>7610</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>21</v>
@@ -10385,7 +10383,7 @@
         <v>45</v>
       </c>
       <c r="J102" s="52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L102" s="102"/>
     </row>
@@ -11790,7 +11788,7 @@
         <v>7613</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>21</v>
@@ -11813,7 +11811,7 @@
         <v>60</v>
       </c>
       <c r="J125" s="52" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L125" s="102"/>
     </row>
@@ -11854,7 +11852,7 @@
         <v>7616</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>21</v>
@@ -11877,7 +11875,7 @@
         <v>60</v>
       </c>
       <c r="J127" s="52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L127" s="102"/>
     </row>
@@ -11980,7 +11978,7 @@
         <v>7626</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>21</v>
@@ -12003,7 +12001,7 @@
         <v>60</v>
       </c>
       <c r="J131" s="52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L131" s="102"/>
     </row>
@@ -12271,7 +12269,7 @@
         <v>6411</v>
       </c>
       <c r="B141" s="53" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C141" s="50" t="s">
         <v>21</v>
@@ -12357,7 +12355,7 @@
         <v>6929</v>
       </c>
       <c r="B144" s="53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C144" s="50" t="s">
         <v>23</v>
@@ -12381,7 +12379,7 @@
         <v>7485</v>
       </c>
       <c r="B145" s="53" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C145" s="50" t="s">
         <v>21</v>
@@ -12400,7 +12398,7 @@
       <c r="H145" s="29"/>
       <c r="I145" s="29"/>
       <c r="J145" s="105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -12409,7 +12407,7 @@
         <v>7647</v>
       </c>
       <c r="B146" s="53" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C146" s="50" t="s">
         <v>21</v>
@@ -12432,7 +12430,7 @@
         <v>30</v>
       </c>
       <c r="J146" s="105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12441,7 +12439,7 @@
         <v>7651</v>
       </c>
       <c r="B147" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C147" s="50" t="s">
         <v>21</v>
@@ -12464,7 +12462,7 @@
         <v>30</v>
       </c>
       <c r="J147" s="105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -12549,7 +12547,7 @@
         <v>6008</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C151" s="50" t="s">
         <v>23</v>
@@ -12572,7 +12570,7 @@
         <v>40</v>
       </c>
       <c r="J151" s="105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -12624,7 +12622,7 @@
         <v>0.18</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" ref="G153:G162" si="29">E153*F153</f>
+        <f t="shared" ref="G153:G161" si="29">E153*F153</f>
         <v>0</v>
       </c>
       <c r="H153" s="14">
@@ -12844,7 +12842,7 @@
         <v>60</v>
       </c>
       <c r="J160" s="52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -12853,7 +12851,7 @@
         <v>7344</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>21</v>
@@ -12879,7 +12877,7 @@
         <v>7345</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>21</v>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0800D2AD-DD5B-43B3-87C5-23165BD6151D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8660D8EB-CA39-4CA5-B4A6-A42F458628BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$415</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$415</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$414</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$414</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -491,7 +491,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="223">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1158,6 +1158,9 @@
   </si>
   <si>
     <t>ХОЧУ ВЕТЧ. МРАМОР. с/н мгс 1/100_45с_Л11</t>
+  </si>
+  <si>
+    <t>ДОМАШНИЙ РЕЦЕПТ Коровино вар п/о_332к</t>
   </si>
 </sst>
 </file>
@@ -8427,7 +8430,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1503"/>
+  <dimension ref="A1:BO1502"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -8639,7 +8642,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="100" t="str">
-        <f t="shared" ref="A12:A72" si="1">RIGHT(D12,4)</f>
+        <f t="shared" ref="A12:A71" si="1">RIGHT(D12,4)</f>
         <v>6220</v>
       </c>
       <c r="B12" s="48" t="s">
@@ -8730,28 +8733,24 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6861</v>
+        <v>7754</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>26</v>
+        <v>222</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="47">
-        <v>1001015646861</v>
+        <v>1001015647754</v>
       </c>
       <c r="E15" s="22"/>
-      <c r="F15" s="21">
-        <v>1.95</v>
-      </c>
+      <c r="F15" s="21"/>
       <c r="G15" s="21">
         <f>E15</f>
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <v>3.9</v>
-      </c>
+      <c r="H15" s="13"/>
       <c r="I15" s="13">
         <v>60</v>
       </c>
@@ -8760,27 +8759,27 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6862</v>
+        <v>6498</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C16" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="47">
-        <v>1001015706862</v>
+        <v>1001012456498</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="21">
-        <v>1.95</v>
+        <v>1</v>
       </c>
       <c r="G16" s="21">
-        <f t="shared" ref="G16:G18" si="2">E16</f>
+        <f t="shared" ref="G16:G17" si="2">E16</f>
         <v>0</v>
       </c>
       <c r="H16" s="13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I16" s="13">
         <v>60</v>
@@ -8790,27 +8789,27 @@
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6498</v>
+        <v>4063</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C17" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="47">
-        <v>1001012456498</v>
+        <v>1001012484063</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="21">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="G17" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H17" s="13">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="I17" s="13">
         <v>60</v>
@@ -8820,27 +8819,27 @@
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>4063</v>
+        <v>6333</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18" s="47">
-        <v>1001012484063</v>
+        <v>1001012486333</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="21">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G18" s="21">
-        <f t="shared" si="2"/>
+        <f>E18*F18</f>
         <v>0</v>
       </c>
       <c r="H18" s="13">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I18" s="13">
         <v>60</v>
@@ -8850,27 +8849,27 @@
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6333</v>
+        <v>4574</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D19" s="47">
-        <v>1001012486333</v>
+        <v>1001012634574</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="21">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G19" s="21">
-        <f>E19*F19</f>
+        <f>E19</f>
         <v>0</v>
       </c>
       <c r="H19" s="13">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I19" s="13">
         <v>60</v>
@@ -8880,27 +8879,27 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>4574</v>
+        <v>7334</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20" s="47">
-        <v>1001012634574</v>
+        <v>1001012637334</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="21">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G20" s="21">
-        <f>E20</f>
+        <f>E20*F20</f>
         <v>0</v>
       </c>
       <c r="H20" s="13">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I20" s="13">
         <v>60</v>
@@ -8910,29 +8909,29 @@
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7334</v>
+        <v>4813</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D21" s="47">
-        <v>1001012637334</v>
+        <v>1001012564813</v>
       </c>
       <c r="E21" s="22"/>
-      <c r="F21" s="21">
-        <v>0.4</v>
+      <c r="F21" s="102">
+        <v>1.35</v>
       </c>
       <c r="G21" s="21">
-        <f>E21*F21</f>
+        <f>E21</f>
         <v>0</v>
       </c>
-      <c r="H21" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="I21" s="13">
+      <c r="H21" s="26">
+        <v>4.05</v>
+      </c>
+      <c r="I21" s="26">
         <v>60</v>
       </c>
       <c r="J21" s="26"/>
@@ -8940,27 +8939,27 @@
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>4813</v>
+        <v>6392</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="C22" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" s="47">
-        <v>1001012564813</v>
+        <v>1001012566392</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="102">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G22" s="21">
-        <f>E22</f>
+        <f>E22*F22</f>
         <v>0</v>
       </c>
       <c r="H22" s="26">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I22" s="26">
         <v>60</v>
@@ -8970,27 +8969,27 @@
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6392</v>
+        <v>5851</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23" s="47">
-        <v>1001012566392</v>
+        <v>1001012505851</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="102">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G23" s="21">
-        <f>E23*F23</f>
+        <f>E23</f>
         <v>0</v>
       </c>
       <c r="H23" s="26">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I23" s="26">
         <v>60</v>
@@ -9000,27 +8999,27 @@
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>5851</v>
+        <v>7632</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="C24" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D24" s="47">
-        <v>1001012505851</v>
+        <v>1001012507632</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="102">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G24" s="21">
-        <f>E24</f>
+        <f>E24*F24</f>
         <v>0</v>
       </c>
       <c r="H24" s="26">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I24" s="26">
         <v>60</v>
@@ -9030,29 +9029,29 @@
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7632</v>
+        <v>4561</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="C25" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D25" s="47">
-        <v>1001012507632</v>
+        <v>1001010014561</v>
       </c>
       <c r="E25" s="22"/>
-      <c r="F25" s="102">
-        <v>0.4</v>
+      <c r="F25" s="21">
+        <v>1.35</v>
       </c>
       <c r="G25" s="21">
-        <f>E25*F25</f>
+        <f t="shared" ref="G25" si="3">E25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="26">
-        <v>3.2</v>
-      </c>
-      <c r="I25" s="26">
+      <c r="H25" s="13">
+        <v>4.05</v>
+      </c>
+      <c r="I25" s="13">
         <v>60</v>
       </c>
       <c r="J25" s="26"/>
@@ -9060,27 +9059,27 @@
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>4561</v>
+        <v>6325</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="C26" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" s="47">
-        <v>1001010014561</v>
+        <v>1001010106325</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="21">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G26" s="21">
-        <f t="shared" ref="G26" si="3">E26</f>
+        <f>E26*F26</f>
         <v>0</v>
       </c>
       <c r="H26" s="13">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I26" s="13">
         <v>60</v>
@@ -9090,29 +9089,29 @@
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6325</v>
+        <v>8014</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>33</v>
+        <v>205</v>
       </c>
       <c r="C27" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" s="47">
-        <v>1001010106325</v>
+        <v>1001010108014</v>
       </c>
       <c r="E27" s="22"/>
-      <c r="F27" s="21">
-        <v>0.4</v>
+      <c r="F27" s="102">
+        <v>1.35</v>
       </c>
       <c r="G27" s="21">
-        <f>E27*F27</f>
+        <f t="shared" ref="G27" si="4">E27</f>
         <v>0</v>
       </c>
-      <c r="H27" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="I27" s="13">
+      <c r="H27" s="26">
+        <v>5.4</v>
+      </c>
+      <c r="I27" s="26">
         <v>60</v>
       </c>
       <c r="J27" s="26"/>
@@ -9120,46 +9119,43 @@
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>8014</v>
+        <v>7514</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C28" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="47">
-        <v>1001010108014</v>
+        <v>1001017557514</v>
       </c>
       <c r="E28" s="22"/>
-      <c r="F28" s="102">
-        <v>1.35</v>
-      </c>
+      <c r="F28" s="102"/>
       <c r="G28" s="21">
-        <f t="shared" ref="G28" si="4">E28</f>
+        <f>E28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="26">
-        <v>5.4</v>
-      </c>
-      <c r="I28" s="26">
-        <v>60</v>
-      </c>
-      <c r="J28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26" t="str">
+        <f>VLOOKUP(D28,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7514</v>
+        <v>7518</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C29" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="47">
-        <v>1001017557514</v>
+        <v>1001017567518</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="102"/>
@@ -9177,50 +9173,53 @@
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7518</v>
+        <v>7343</v>
       </c>
       <c r="B30" s="48" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D30" s="47">
-        <v>1001017567518</v>
+        <v>1001016747343</v>
       </c>
       <c r="E30" s="22"/>
-      <c r="F30" s="102"/>
+      <c r="F30" s="102">
+        <v>0.4</v>
+      </c>
       <c r="G30" s="21">
-        <f>E30</f>
+        <f t="shared" ref="G30:G32" si="5">E30*F30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26" t="str">
-        <f>VLOOKUP(D30,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H30" s="26">
+        <v>3.2</v>
+      </c>
+      <c r="I30" s="26">
+        <v>60</v>
+      </c>
+      <c r="J30" s="26"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7343</v>
+        <v>6797</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="47">
-        <v>1001016747343</v>
+        <v>1001015026797</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="102">
         <v>0.4</v>
       </c>
       <c r="G31" s="21">
-        <f t="shared" ref="G31:G33" si="5">E31*F31</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H31" s="26">
@@ -9231,136 +9230,136 @@
       </c>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6797</v>
+        <v>7231</v>
       </c>
       <c r="B32" s="48" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="C32" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="47">
-        <v>1001015026797</v>
+        <v>1001013957231</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="102">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G32" s="21">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H32" s="26">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I32" s="26">
         <v>60</v>
       </c>
       <c r="J32" s="26"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="100" t="str">
+    <row r="33" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="40"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7231</v>
-      </c>
-      <c r="B33" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="46" t="s">
+        <v>6602</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="47">
-        <v>1001013957231</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="102">
-        <v>0.3</v>
-      </c>
-      <c r="G33" s="21">
-        <f t="shared" si="5"/>
+      <c r="D34" s="47">
+        <v>1001021966602</v>
+      </c>
+      <c r="E34" s="22"/>
+      <c r="F34" s="102">
+        <v>0.35</v>
+      </c>
+      <c r="G34" s="21">
+        <f t="shared" ref="G34:G38" si="6">E34*F34</f>
         <v>0</v>
       </c>
-      <c r="H33" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="I33" s="26">
-        <v>60</v>
-      </c>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="40"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H34" s="26">
+        <v>2.8</v>
+      </c>
+      <c r="I34" s="26">
+        <v>45</v>
+      </c>
+      <c r="J34" s="26"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6602</v>
+        <v>7601</v>
       </c>
       <c r="B35" s="48" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="47">
-        <v>1001021966602</v>
+        <v>1001025767601</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="102">
-        <v>0.35</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G35" s="21">
-        <f t="shared" ref="G35:G39" si="6">E35*F35</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="26">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="I35" s="26">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J35" s="26"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7601</v>
+        <v>7461</v>
       </c>
       <c r="B36" s="48" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C36" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="47">
-        <v>1001025767601</v>
+        <v>1001025767461</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="102">
-        <v>0.26400000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="G36" s="21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="26">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="I36" s="26">
         <v>30</v>
@@ -9370,83 +9369,83 @@
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7461</v>
+        <v>7040</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C37" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="47">
-        <v>1001025767461</v>
+        <v>1001025027040</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="102">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="G37" s="21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H37" s="26">
-        <v>1.98</v>
-      </c>
-      <c r="I37" s="26">
-        <v>30</v>
-      </c>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
       <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7040</v>
+        <v>6759</v>
       </c>
       <c r="B38" s="48" t="s">
-        <v>203</v>
+        <v>42</v>
       </c>
       <c r="C38" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="47">
-        <v>1001025027040</v>
+        <v>1001020836759</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="102">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="G38" s="21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
+      <c r="H38" s="26">
+        <v>2.8</v>
+      </c>
+      <c r="I38" s="26">
+        <v>30</v>
+      </c>
       <c r="J38" s="26"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6759</v>
+        <v>6761</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C39" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D39" s="47">
-        <v>1001020836759</v>
+        <v>1001020836761</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="102">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G39" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G39:G40" si="7">E39</f>
         <v>0</v>
       </c>
       <c r="H39" s="26">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I39" s="26">
         <v>30</v>
@@ -9456,57 +9455,57 @@
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6761</v>
+        <v>6829</v>
       </c>
       <c r="B40" s="48" t="s">
-        <v>53</v>
+        <v>182</v>
       </c>
       <c r="C40" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="47">
-        <v>1001020836761</v>
+        <v>1001024976829</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="102">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="G40" s="21">
-        <f t="shared" ref="G40:G41" si="7">E40</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H40" s="26">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="I40" s="26">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J40" s="26"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6829</v>
+        <v>6616</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>182</v>
+        <v>43</v>
       </c>
       <c r="C41" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D41" s="47">
-        <v>1001024976829</v>
+        <v>1001024976616</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="102">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="G41" s="21">
-        <f t="shared" si="7"/>
+        <f>E41*F41</f>
         <v>0</v>
       </c>
       <c r="H41" s="26">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="I41" s="26">
         <v>45</v>
@@ -9516,57 +9515,57 @@
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6616</v>
+        <v>7075</v>
       </c>
       <c r="B42" s="48" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C42" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D42" s="47">
-        <v>1001024976616</v>
+        <v>1001022657075</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="102">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="G42" s="21">
-        <f>E42*F42</f>
+        <f>E42</f>
         <v>0</v>
       </c>
       <c r="H42" s="26">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I42" s="26">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J42" s="26"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7075</v>
+        <v>7074</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>50</v>
+        <v>183</v>
       </c>
       <c r="C43" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D43" s="47">
-        <v>1001022657075</v>
+        <v>1001022657074</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="102">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="G43" s="21">
-        <f>E43</f>
+        <f t="shared" ref="G43:G46" si="8">E43*F43</f>
         <v>0</v>
       </c>
       <c r="H43" s="26">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I43" s="26">
         <v>50</v>
@@ -9576,27 +9575,27 @@
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7074</v>
+        <v>7073</v>
       </c>
       <c r="B44" s="48" t="s">
-        <v>183</v>
+        <v>51</v>
       </c>
       <c r="C44" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="47">
-        <v>1001022657074</v>
+        <v>1001022657073</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="102">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="G44" s="21">
-        <f t="shared" ref="G44:G47" si="8">E44*F44</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H44" s="26">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="I44" s="26">
         <v>50</v>
@@ -9606,57 +9605,57 @@
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7073</v>
+        <v>6724</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="47">
-        <v>1001022657073</v>
+        <v>1001020836724</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="102">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="G45" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H45" s="26">
-        <v>2.8</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I45" s="26">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J45" s="26"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6724</v>
+        <v>5819</v>
       </c>
       <c r="B46" s="48" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C46" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="47">
-        <v>1001020836724</v>
+        <v>1001022725819</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="102">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G46" s="21">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H46" s="26">
-        <v>4.0999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="I46" s="26">
         <v>45</v>
@@ -9666,27 +9665,27 @@
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>5819</v>
+        <v>6303</v>
       </c>
       <c r="B47" s="48" t="s">
-        <v>39</v>
+        <v>184</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D47" s="47">
-        <v>1001022725819</v>
+        <v>1001022726303</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="102">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G47" s="21">
-        <f t="shared" si="8"/>
+        <f>E47</f>
         <v>0</v>
       </c>
       <c r="H47" s="26">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="I47" s="26">
         <v>45</v>
@@ -9696,57 +9695,57 @@
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6303</v>
+        <v>7255</v>
       </c>
       <c r="B48" s="48" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="C48" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D48" s="47">
-        <v>1001022726303</v>
+        <v>1001025507255</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="102">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G48" s="21">
-        <f>E48</f>
+        <f>E48*F48</f>
         <v>0</v>
       </c>
       <c r="H48" s="26">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="I48" s="26">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J48" s="26"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7255</v>
+        <v>7271</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="C49" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D49" s="47">
-        <v>1001025507255</v>
+        <v>1001025507271</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="102">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G49" s="21">
-        <f>E49*F49</f>
+        <f>E49</f>
         <v>0</v>
       </c>
       <c r="H49" s="26">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I49" s="26">
         <v>50</v>
@@ -9756,57 +9755,57 @@
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7271</v>
+        <v>6765</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="C50" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D50" s="47">
-        <v>1001025507271</v>
+        <v>1001023696765</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="102">
-        <v>1.5</v>
+        <v>0.36</v>
       </c>
       <c r="G50" s="21">
-        <f>E50</f>
+        <f>E50*F50</f>
         <v>0</v>
       </c>
       <c r="H50" s="26">
-        <v>6</v>
+        <v>2.16</v>
       </c>
       <c r="I50" s="26">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J50" s="26"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6765</v>
+        <v>6767</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C51" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D51" s="47">
-        <v>1001023696765</v>
+        <v>1001023696767</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="102">
-        <v>0.36</v>
+        <v>1.04</v>
       </c>
       <c r="G51" s="21">
-        <f>E51*F51</f>
+        <f>E51</f>
         <v>0</v>
       </c>
       <c r="H51" s="26">
-        <v>2.16</v>
+        <v>4.16</v>
       </c>
       <c r="I51" s="26">
         <v>45</v>
@@ -9816,27 +9815,27 @@
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6767</v>
+        <v>6475</v>
       </c>
       <c r="B52" s="48" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C52" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D52" s="47">
-        <v>1001023696767</v>
+        <v>1001025176475</v>
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="102">
-        <v>1.04</v>
+        <v>0.4</v>
       </c>
       <c r="G52" s="21">
-        <f>E52</f>
+        <f>E52*F52</f>
         <v>0</v>
       </c>
       <c r="H52" s="26">
-        <v>4.16</v>
+        <v>2.4</v>
       </c>
       <c r="I52" s="26">
         <v>45</v>
@@ -9846,57 +9845,57 @@
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6475</v>
+        <v>7083</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="C53" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D53" s="47">
-        <v>1001025176475</v>
+        <v>1001022467083</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="102">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G53" s="21">
-        <f>E53*F53</f>
+        <f>E53</f>
         <v>0</v>
       </c>
       <c r="H53" s="26">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I53" s="26">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J53" s="26"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7083</v>
+        <v>7080</v>
       </c>
       <c r="B54" s="48" t="s">
-        <v>186</v>
+        <v>54</v>
       </c>
       <c r="C54" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D54" s="47">
-        <v>1001022467083</v>
+        <v>1001022467080</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="102">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G54" s="21">
-        <f>E54</f>
+        <f t="shared" ref="G54:G56" si="9">E54*F54</f>
         <v>0</v>
       </c>
       <c r="H54" s="26">
-        <v>6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I54" s="26">
         <v>50</v>
@@ -9906,27 +9905,27 @@
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7080</v>
+        <v>7276</v>
       </c>
       <c r="B55" s="48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C55" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="47">
-        <v>1001022467080</v>
+        <v>1001022467276</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="102">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="G55" s="21">
-        <f t="shared" ref="G55:G57" si="9">E55*F55</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H55" s="26">
-        <v>4.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I55" s="26">
         <v>50</v>
@@ -9936,59 +9935,59 @@
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7276</v>
+        <v>6762</v>
       </c>
       <c r="B56" s="48" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C56" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="47">
-        <v>1001022467276</v>
+        <v>1001020846762</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="102">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="G56" s="21">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H56" s="26">
-        <v>2.1</v>
+        <v>3.28</v>
       </c>
       <c r="I56" s="26">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J56" s="26"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6762</v>
+        <v>6764</v>
       </c>
       <c r="B57" s="48" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C57" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D57" s="47">
-        <v>1001020846762</v>
+        <v>1001020846764</v>
       </c>
       <c r="E57" s="22"/>
-      <c r="F57" s="102">
-        <v>0.41</v>
+      <c r="F57" s="21">
+        <v>1</v>
       </c>
       <c r="G57" s="21">
-        <f t="shared" si="9"/>
+        <f>E57</f>
         <v>0</v>
       </c>
-      <c r="H57" s="26">
-        <v>3.28</v>
-      </c>
-      <c r="I57" s="26">
+      <c r="H57" s="13">
+        <v>4</v>
+      </c>
+      <c r="I57" s="13">
         <v>45</v>
       </c>
       <c r="J57" s="26"/>
@@ -9996,57 +9995,57 @@
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6764</v>
+        <v>7066</v>
       </c>
       <c r="B58" s="48" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C58" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D58" s="47">
-        <v>1001020846764</v>
+        <v>1001022377066</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="21">
-        <v>1</v>
+        <v>0.41</v>
       </c>
       <c r="G58" s="21">
-        <f>E58</f>
+        <f>E58*F58</f>
         <v>0</v>
       </c>
       <c r="H58" s="13">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I58" s="13">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J58" s="26"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7066</v>
+        <v>7070</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C59" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D59" s="47">
-        <v>1001022377066</v>
+        <v>1001022377070</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="21">
-        <v>0.41</v>
+        <v>1.5</v>
       </c>
       <c r="G59" s="21">
-        <f>E59*F59</f>
+        <f>E59</f>
         <v>0</v>
       </c>
       <c r="H59" s="13">
-        <v>4.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="I59" s="13">
         <v>50</v>
@@ -10056,86 +10055,86 @@
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7070</v>
+        <v>7490</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="C60" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D60" s="47">
-        <v>1001022377070</v>
+        <v>1001027417490</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="21">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G60" s="21">
-        <f>E60</f>
+        <f>E60*F60</f>
         <v>0</v>
       </c>
-      <c r="H60" s="13">
-        <v>6</v>
-      </c>
-      <c r="I60" s="13">
-        <v>50</v>
-      </c>
-      <c r="J60" s="26"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="26" t="str">
+        <f>VLOOKUP(D60,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 6713</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7490</v>
+        <v>6661</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="C61" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D61" s="47">
-        <v>1001027417490</v>
+        <v>1001022246661</v>
       </c>
       <c r="E61" s="22"/>
       <c r="F61" s="21">
-        <v>0.41</v>
+        <v>1.5</v>
       </c>
       <c r="G61" s="21">
-        <f>E61*F61</f>
+        <f t="shared" ref="G61:G62" si="10">E61</f>
         <v>0</v>
       </c>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="26" t="str">
-        <f>VLOOKUP(D61,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 6713</v>
-      </c>
+      <c r="H61" s="13">
+        <v>6</v>
+      </c>
+      <c r="I61" s="13">
+        <v>45</v>
+      </c>
+      <c r="J61" s="26"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6661</v>
+        <v>6254</v>
       </c>
       <c r="B62" s="48" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C62" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D62" s="47">
-        <v>1001022246661</v>
+        <v>1001022556254</v>
       </c>
       <c r="E62" s="22"/>
       <c r="F62" s="21">
         <v>1.5</v>
       </c>
       <c r="G62" s="21">
-        <f t="shared" ref="G62:G63" si="10">E62</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H62" s="13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I62" s="13">
         <v>45</v>
@@ -10145,135 +10144,135 @@
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6254</v>
+        <v>6837</v>
       </c>
       <c r="B63" s="48" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="C63" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D63" s="47">
-        <v>1001022556254</v>
+        <v>1001022556837</v>
       </c>
       <c r="E63" s="22"/>
       <c r="F63" s="21">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G63" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="G63:G64" si="11">E63*F63</f>
         <v>0</v>
       </c>
       <c r="H63" s="13">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="I63" s="13">
         <v>45</v>
       </c>
       <c r="J63" s="26"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6837</v>
+        <v>7044</v>
       </c>
       <c r="B64" s="48" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="C64" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D64" s="47">
-        <v>1001022556837</v>
+        <v>1001025167044</v>
       </c>
       <c r="E64" s="22"/>
       <c r="F64" s="21">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="G64" s="21">
-        <f t="shared" ref="G64:G65" si="11">E64*F64</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H64" s="13">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="I64" s="13">
         <v>45</v>
       </c>
       <c r="J64" s="26"/>
     </row>
-    <row r="65" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="100" t="str">
+    <row r="65" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="40"/>
+    </row>
+    <row r="66" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7044</v>
-      </c>
-      <c r="B65" s="48" t="s">
-        <v>190</v>
-      </c>
-      <c r="C65" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="D65" s="47">
-        <v>1001025167044</v>
-      </c>
-      <c r="E65" s="22"/>
-      <c r="F65" s="21">
-        <v>0.32</v>
-      </c>
-      <c r="G65" s="21">
-        <f t="shared" si="11"/>
+        <v>6550</v>
+      </c>
+      <c r="B66" s="99" t="s">
+        <v>174</v>
+      </c>
+      <c r="C66" s="103" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="47">
+        <v>1001032736550</v>
+      </c>
+      <c r="E66" s="22"/>
+      <c r="F66" s="102">
+        <v>1</v>
+      </c>
+      <c r="G66" s="21">
+        <f t="shared" ref="G66:G69" si="12">E66</f>
         <v>0</v>
       </c>
-      <c r="H65" s="13">
-        <v>2.56</v>
-      </c>
-      <c r="I65" s="13">
+      <c r="H66" s="26">
+        <v>3</v>
+      </c>
+      <c r="I66" s="26">
         <v>45</v>
       </c>
-      <c r="J65" s="26"/>
-    </row>
-    <row r="66" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B66" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39"/>
-      <c r="I66" s="39"/>
-      <c r="J66" s="40"/>
-    </row>
-    <row r="67" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J66" s="26"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6550</v>
+        <v>6608</v>
       </c>
       <c r="B67" s="99" t="s">
-        <v>174</v>
-      </c>
-      <c r="C67" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D67" s="47">
-        <v>1001032736550</v>
+        <v>1001033856608</v>
       </c>
       <c r="E67" s="22"/>
-      <c r="F67" s="102">
+      <c r="F67" s="21">
         <v>1</v>
       </c>
       <c r="G67" s="21">
-        <f t="shared" ref="G67:G70" si="12">E67</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H67" s="26">
+      <c r="H67" s="13">
         <v>3</v>
       </c>
-      <c r="I67" s="26">
+      <c r="I67" s="13">
         <v>45</v>
       </c>
       <c r="J67" s="26"/>
@@ -10281,16 +10280,16 @@
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6608</v>
+        <v>7001</v>
       </c>
       <c r="B68" s="99" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C68" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D68" s="47">
-        <v>1001033856608</v>
+        <v>1001035937001</v>
       </c>
       <c r="E68" s="22"/>
       <c r="F68" s="21">
@@ -10311,16 +10310,16 @@
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>7001</v>
+        <v>6527</v>
       </c>
       <c r="B69" s="99" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="C69" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D69" s="47">
-        <v>1001035937001</v>
+        <v>1001031076527</v>
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="21">
@@ -10341,133 +10340,133 @@
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6527</v>
+        <v>6609</v>
       </c>
       <c r="B70" s="99" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C70" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D70" s="47">
-        <v>1001031076527</v>
+        <v>1001033856609</v>
       </c>
       <c r="E70" s="22"/>
       <c r="F70" s="21">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G70" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="G70:G71" si="13">E70*F70</f>
         <v>0</v>
       </c>
       <c r="H70" s="13">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="I70" s="13">
         <v>45</v>
       </c>
       <c r="J70" s="26"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6609</v>
+        <v>7059</v>
       </c>
       <c r="B71" s="99" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C71" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D71" s="47">
-        <v>1001033856609</v>
+        <v>1001035277059</v>
       </c>
       <c r="E71" s="22"/>
       <c r="F71" s="21">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G71" s="21">
-        <f t="shared" ref="G71:G72" si="13">E71*F71</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H71" s="13">
         <v>2.4</v>
       </c>
       <c r="I71" s="13">
+        <v>60</v>
+      </c>
+      <c r="J71" s="26"/>
+    </row>
+    <row r="72" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B72" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="40"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="100" t="str">
+        <f t="shared" ref="A73:A97" si="14">RIGHT(D73,4)</f>
+        <v>7564</v>
+      </c>
+      <c r="B73" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" s="47">
+        <v>1001303637564</v>
+      </c>
+      <c r="E73" s="22"/>
+      <c r="F73" s="21">
+        <v>0.84</v>
+      </c>
+      <c r="G73" s="21">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="13">
+        <v>5.04</v>
+      </c>
+      <c r="I73" s="13">
         <v>45</v>
       </c>
-      <c r="J71" s="26"/>
-    </row>
-    <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="100" t="str">
-        <f t="shared" si="1"/>
-        <v>7059</v>
-      </c>
-      <c r="B72" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="C72" s="46" t="s">
+      <c r="J73" s="26"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="100" t="str">
+        <f t="shared" si="14"/>
+        <v>7603</v>
+      </c>
+      <c r="B74" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="47">
-        <v>1001035277059</v>
-      </c>
-      <c r="E72" s="22"/>
-      <c r="F72" s="21">
-        <v>0.3</v>
-      </c>
-      <c r="G72" s="21">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="13">
-        <v>2.4</v>
-      </c>
-      <c r="I72" s="13">
-        <v>60</v>
-      </c>
-      <c r="J72" s="26"/>
-    </row>
-    <row r="73" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B73" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
-      <c r="J73" s="40"/>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="100" t="str">
-        <f t="shared" ref="A74:A98" si="14">RIGHT(D74,4)</f>
-        <v>7564</v>
-      </c>
-      <c r="B74" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C74" s="46" t="s">
-        <v>23</v>
-      </c>
       <c r="D74" s="47">
-        <v>1001303637564</v>
+        <v>1001303637603</v>
       </c>
       <c r="E74" s="22"/>
       <c r="F74" s="21">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="G74" s="21">
-        <f>E74</f>
+        <f t="shared" ref="G74:G86" si="15">E74*F74</f>
         <v>0</v>
       </c>
       <c r="H74" s="13">
-        <v>5.04</v>
+        <v>2.64</v>
       </c>
       <c r="I74" s="13">
         <v>45</v>
@@ -10477,106 +10476,106 @@
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7603</v>
+        <v>7149</v>
       </c>
       <c r="B75" s="48" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="C75" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D75" s="47">
-        <v>1001303637603</v>
+        <v>1001303637149</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="21">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="G75" s="21">
-        <f t="shared" ref="G75:G87" si="15">E75*F75</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H75" s="13">
-        <v>2.64</v>
+        <v>5.04</v>
       </c>
       <c r="I75" s="13">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J75" s="26"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7149</v>
+        <v>7233</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="C76" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D76" s="47">
-        <v>1001303637149</v>
+        <v>1001303637233</v>
       </c>
       <c r="E76" s="22"/>
-      <c r="F76" s="21">
-        <v>0.84</v>
+      <c r="F76" s="102">
+        <v>0.31</v>
       </c>
       <c r="G76" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H76" s="13">
-        <v>5.04</v>
-      </c>
-      <c r="I76" s="13">
-        <v>50</v>
+      <c r="H76" s="26">
+        <v>2.48</v>
+      </c>
+      <c r="I76" s="26">
+        <v>45</v>
       </c>
       <c r="J76" s="26"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7233</v>
+        <v>7232</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="C77" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D77" s="47">
-        <v>1001303637233</v>
+        <v>1001302277232</v>
       </c>
       <c r="E77" s="22"/>
       <c r="F77" s="102">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G77" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H77" s="26">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I77" s="26">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J77" s="26"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7232</v>
+        <v>7241</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C78" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D78" s="47">
-        <v>1001302277232</v>
+        <v>1001303107241</v>
       </c>
       <c r="E78" s="22"/>
       <c r="F78" s="102">
@@ -10590,34 +10589,34 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I78" s="26">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J78" s="26"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7241</v>
+        <v>7133</v>
       </c>
       <c r="B79" s="48" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D79" s="47">
-        <v>1001303107241</v>
+        <v>1001300367133</v>
       </c>
       <c r="E79" s="22"/>
       <c r="F79" s="102">
-        <v>0.28000000000000003</v>
+        <v>0.84</v>
       </c>
       <c r="G79" s="21">
-        <f t="shared" si="15"/>
+        <f>E79</f>
         <v>0</v>
       </c>
       <c r="H79" s="26">
-        <v>2.2400000000000002</v>
+        <v>5.04</v>
       </c>
       <c r="I79" s="26">
         <v>45</v>
@@ -10627,111 +10626,111 @@
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7133</v>
+        <v>6946</v>
       </c>
       <c r="B80" s="48" t="s">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="C80" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D80" s="47">
-        <v>1001300367133</v>
+        <v>1001300456946</v>
       </c>
       <c r="E80" s="22"/>
-      <c r="F80" s="102">
-        <v>0.84</v>
-      </c>
+      <c r="F80" s="102"/>
       <c r="G80" s="21">
         <f>E80</f>
         <v>0</v>
       </c>
-      <c r="H80" s="26">
-        <v>5.04</v>
-      </c>
-      <c r="I80" s="26">
-        <v>45</v>
-      </c>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
       <c r="J80" s="26"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6946</v>
+        <v>6807</v>
       </c>
       <c r="B81" s="48" t="s">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="C81" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D81" s="47">
-        <v>1001300456946</v>
+        <v>1001300366807</v>
       </c>
       <c r="E81" s="22"/>
-      <c r="F81" s="102"/>
+      <c r="F81" s="102">
+        <v>0.33</v>
+      </c>
       <c r="G81" s="21">
-        <f>E81</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H81" s="26"/>
-      <c r="I81" s="26"/>
+      <c r="H81" s="26">
+        <v>2.64</v>
+      </c>
+      <c r="I81" s="26">
+        <v>45</v>
+      </c>
       <c r="J81" s="26"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6807</v>
+        <v>7154</v>
       </c>
       <c r="B82" s="48" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C82" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="47">
-        <v>1001300366807</v>
+        <v>1001300387154</v>
       </c>
       <c r="E82" s="22"/>
-      <c r="F82" s="102">
-        <v>0.33</v>
+      <c r="F82" s="21">
+        <v>0.35</v>
       </c>
       <c r="G82" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H82" s="26">
-        <v>2.64</v>
-      </c>
-      <c r="I82" s="26">
-        <v>45</v>
+      <c r="H82" s="13">
+        <v>2.8</v>
+      </c>
+      <c r="I82" s="13">
+        <v>50</v>
       </c>
       <c r="J82" s="26"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7154</v>
+        <v>7157</v>
       </c>
       <c r="B83" s="48" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C83" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D83" s="47">
-        <v>1001300387154</v>
+        <v>1001300387157</v>
       </c>
       <c r="E83" s="22"/>
       <c r="F83" s="21">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="G83" s="21">
-        <f t="shared" si="15"/>
+        <f>E83</f>
         <v>0</v>
       </c>
       <c r="H83" s="13">
-        <v>2.8</v>
+        <v>5.04</v>
       </c>
       <c r="I83" s="13">
         <v>50</v>
@@ -10741,84 +10740,84 @@
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7157</v>
+        <v>7562</v>
       </c>
       <c r="B84" s="48" t="s">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="C84" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D84" s="47">
-        <v>1001300387157</v>
+        <v>1001307587562</v>
       </c>
       <c r="E84" s="22"/>
-      <c r="F84" s="21">
-        <v>0.63</v>
-      </c>
+      <c r="F84" s="21"/>
       <c r="G84" s="21">
         <f>E84</f>
         <v>0</v>
       </c>
-      <c r="H84" s="13">
-        <v>5.04</v>
-      </c>
-      <c r="I84" s="13">
-        <v>50</v>
-      </c>
-      <c r="J84" s="26"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="26" t="str">
+        <f>VLOOKUP(D84,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7562</v>
+        <v>7236</v>
       </c>
       <c r="B85" s="48" t="s">
-        <v>212</v>
+        <v>69</v>
       </c>
       <c r="C85" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D85" s="47">
-        <v>1001307587562</v>
+        <v>1001304507236</v>
       </c>
       <c r="E85" s="22"/>
-      <c r="F85" s="21"/>
+      <c r="F85" s="21">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="G85" s="21">
-        <f>E85</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="26" t="str">
-        <f>VLOOKUP(D85,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H85" s="13">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I85" s="13">
+        <v>45</v>
+      </c>
+      <c r="J85" s="26"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7236</v>
-      </c>
-      <c r="B86" s="48" t="s">
-        <v>69</v>
+        <v>6787</v>
+      </c>
+      <c r="B86" s="104" t="s">
+        <v>66</v>
       </c>
       <c r="C86" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D86" s="47">
-        <v>1001304507236</v>
+        <v>1001300456787</v>
       </c>
       <c r="E86" s="22"/>
       <c r="F86" s="21">
-        <v>0.28000000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="G86" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H86" s="13">
-        <v>2.2400000000000002</v>
+        <v>2.64</v>
       </c>
       <c r="I86" s="13">
         <v>45</v>
@@ -10828,57 +10827,57 @@
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6787</v>
+        <v>7166</v>
       </c>
       <c r="B87" s="104" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C87" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D87" s="47">
-        <v>1001300456787</v>
+        <v>1001303987166</v>
       </c>
       <c r="E87" s="22"/>
       <c r="F87" s="21">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="G87" s="21">
-        <f t="shared" si="15"/>
+        <f>E87</f>
         <v>0</v>
       </c>
       <c r="H87" s="13">
-        <v>2.64</v>
+        <v>5.6</v>
       </c>
       <c r="I87" s="13">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J87" s="26"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7166</v>
-      </c>
-      <c r="B88" s="104" t="s">
-        <v>72</v>
+        <v>7169</v>
+      </c>
+      <c r="B88" s="48" t="s">
+        <v>71</v>
       </c>
       <c r="C88" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D88" s="47">
-        <v>1001303987166</v>
+        <v>1001303987169</v>
       </c>
       <c r="E88" s="22"/>
       <c r="F88" s="21">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="G88" s="21">
-        <f>E88</f>
+        <f>E88*F88</f>
         <v>0</v>
       </c>
       <c r="H88" s="13">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="I88" s="13">
         <v>50</v>
@@ -10888,16 +10887,16 @@
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7169</v>
+        <v>7156</v>
       </c>
       <c r="B89" s="48" t="s">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="C89" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D89" s="47">
-        <v>1001303987169</v>
+        <v>1001304237156</v>
       </c>
       <c r="E89" s="22"/>
       <c r="F89" s="21">
@@ -10907,67 +10906,67 @@
         <f>E89*F89</f>
         <v>0</v>
       </c>
-      <c r="H89" s="13">
-        <v>2.8</v>
-      </c>
-      <c r="I89" s="13">
-        <v>50</v>
-      </c>
-      <c r="J89" s="26"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="26" t="str">
+        <f>VLOOKUP(D89,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7156</v>
+        <v>5544</v>
       </c>
       <c r="B90" s="48" t="s">
-        <v>208</v>
+        <v>73</v>
       </c>
       <c r="C90" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D90" s="47">
-        <v>1001304237156</v>
+        <v>1001051875544</v>
       </c>
       <c r="E90" s="22"/>
       <c r="F90" s="21">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G90" s="21">
-        <f>E90*F90</f>
+        <f>E90</f>
         <v>0</v>
       </c>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="26" t="str">
-        <f>VLOOKUP(D90,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H90" s="13">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="I90" s="13">
+        <v>45</v>
+      </c>
+      <c r="J90" s="26"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>5544</v>
+        <v>6697</v>
       </c>
       <c r="B91" s="48" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C91" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D91" s="47">
-        <v>1001051875544</v>
+        <v>1001301876697</v>
       </c>
       <c r="E91" s="22"/>
       <c r="F91" s="21">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G91" s="21">
-        <f>E91</f>
+        <f t="shared" ref="G91:G97" si="16">E91*F91</f>
         <v>0</v>
       </c>
       <c r="H91" s="13">
-        <v>4.8600000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="I91" s="13">
         <v>45</v>
@@ -10977,27 +10976,27 @@
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6697</v>
+        <v>7238</v>
       </c>
       <c r="B92" s="48" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="C92" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="47">
-        <v>1001301876697</v>
+        <v>1001305197238</v>
       </c>
       <c r="E92" s="22"/>
       <c r="F92" s="21">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G92" s="21">
-        <f t="shared" ref="G92:G98" si="16">E92*F92</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H92" s="13">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I92" s="13">
         <v>45</v>
@@ -11007,16 +11006,16 @@
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7238</v>
+        <v>7516</v>
       </c>
       <c r="B93" s="48" t="s">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="C93" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D93" s="47">
-        <v>1001305197238</v>
+        <v>1001307107516</v>
       </c>
       <c r="E93" s="22"/>
       <c r="F93" s="21">
@@ -11026,31 +11025,30 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H93" s="13">
-        <v>2.48</v>
-      </c>
-      <c r="I93" s="13">
-        <v>45</v>
-      </c>
-      <c r="J93" s="26"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="26" t="str">
+        <f>VLOOKUP(D93,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7516</v>
+        <v>7710</v>
       </c>
       <c r="B94" s="48" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C94" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D94" s="47">
-        <v>1001307107516</v>
+        <v>1001307587710</v>
       </c>
       <c r="E94" s="22"/>
       <c r="F94" s="21">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="G94" s="21">
         <f t="shared" si="16"/>
@@ -11066,20 +11064,20 @@
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7710</v>
+        <v>7513</v>
       </c>
       <c r="B95" s="48" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C95" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D95" s="47">
-        <v>1001307587710</v>
+        <v>1001307077513</v>
       </c>
       <c r="E95" s="22"/>
       <c r="F95" s="21">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="G95" s="21">
         <f t="shared" si="16"/>
@@ -11095,134 +11093,135 @@
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7177</v>
       </c>
       <c r="B96" s="48" t="s">
-        <v>211</v>
+        <v>135</v>
       </c>
       <c r="C96" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D96" s="47">
-        <v>1001307077513</v>
+        <v>1001302347177</v>
       </c>
       <c r="E96" s="22"/>
       <c r="F96" s="21">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="G96" s="21">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="26" t="str">
-        <f>VLOOKUP(D96,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H96" s="13">
+        <v>2.8</v>
+      </c>
+      <c r="I96" s="13">
+        <v>50</v>
+      </c>
+      <c r="J96" s="26"/>
+    </row>
+    <row r="97" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7177</v>
+        <v>7608</v>
       </c>
       <c r="B97" s="48" t="s">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="C97" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D97" s="47">
-        <v>1001302347177</v>
+        <v>1001304197608</v>
       </c>
       <c r="E97" s="22"/>
       <c r="F97" s="21">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="G97" s="21">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H97" s="13">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="I97" s="13">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J97" s="26"/>
     </row>
-    <row r="98" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="100" t="str">
-        <f t="shared" si="14"/>
-        <v>7608</v>
-      </c>
-      <c r="B98" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="C98" s="46" t="s">
+    <row r="98" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B98" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98" s="39"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="39"/>
+      <c r="F98" s="38"/>
+      <c r="G98" s="39"/>
+      <c r="H98" s="39"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="40"/>
+    </row>
+    <row r="99" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="100" t="str">
+        <f t="shared" ref="A99:A125" si="17">RIGHT(D99,4)</f>
+        <v>3986</v>
+      </c>
+      <c r="B99" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C99" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="D98" s="47">
-        <v>1001304197608</v>
-      </c>
-      <c r="E98" s="22"/>
-      <c r="F98" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="G98" s="21">
-        <f t="shared" si="16"/>
+      <c r="D99" s="47">
+        <v>1001061973986</v>
+      </c>
+      <c r="E99" s="22"/>
+      <c r="F99" s="102">
+        <v>0.25</v>
+      </c>
+      <c r="G99" s="21">
+        <f t="shared" ref="G99:G104" si="18">E99*F99</f>
         <v>0</v>
       </c>
-      <c r="H98" s="13">
-        <v>1</v>
-      </c>
-      <c r="I98" s="13">
-        <v>45</v>
-      </c>
-      <c r="J98" s="26"/>
-    </row>
-    <row r="99" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B99" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C99" s="39"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="39"/>
-      <c r="F99" s="38"/>
-      <c r="G99" s="39"/>
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
-      <c r="J99" s="40"/>
-    </row>
-    <row r="100" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H99" s="105">
+        <v>2</v>
+      </c>
+      <c r="I99" s="106">
+        <v>120</v>
+      </c>
+      <c r="J99" s="26"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="100" t="str">
-        <f t="shared" ref="A100:A126" si="17">RIGHT(D100,4)</f>
-        <v>3986</v>
+        <f t="shared" si="17"/>
+        <v>5931</v>
       </c>
       <c r="B100" s="48" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C100" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="47">
-        <v>1001061973986</v>
+        <v>1001060755931</v>
       </c>
       <c r="E100" s="22"/>
-      <c r="F100" s="102">
-        <v>0.25</v>
+      <c r="F100" s="21">
+        <v>0.22</v>
       </c>
       <c r="G100" s="21">
-        <f t="shared" ref="G100:G105" si="18">E100*F100</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H100" s="105">
-        <v>2</v>
-      </c>
-      <c r="I100" s="106">
+      <c r="H100" s="91">
+        <v>1.76</v>
+      </c>
+      <c r="I100" s="13">
         <v>120</v>
       </c>
       <c r="J100" s="26"/>
@@ -11230,84 +11229,84 @@
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>5931</v>
+        <v>7700</v>
       </c>
       <c r="B101" s="48" t="s">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="C101" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D101" s="47">
-        <v>1001060755931</v>
+        <v>1001067977700</v>
       </c>
       <c r="E101" s="22"/>
-      <c r="F101" s="21">
-        <v>0.22</v>
-      </c>
+      <c r="F101" s="21"/>
       <c r="G101" s="21">
-        <f t="shared" si="18"/>
+        <f>E101</f>
         <v>0</v>
       </c>
-      <c r="H101" s="91">
-        <v>1.76</v>
-      </c>
-      <c r="I101" s="13">
-        <v>120</v>
-      </c>
-      <c r="J101" s="26"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="26" t="str">
+        <f>VLOOKUP(D101,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 5708</v>
+      </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7700</v>
+        <v>3287</v>
       </c>
       <c r="B102" s="48" t="s">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="C102" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D102" s="47">
-        <v>1001067977700</v>
+        <v>1001060763287</v>
       </c>
       <c r="E102" s="22"/>
-      <c r="F102" s="21"/>
+      <c r="F102" s="21">
+        <v>0.48799999999999999</v>
+      </c>
       <c r="G102" s="21">
-        <f>E102</f>
+        <f t="shared" ref="G102" si="19">E102</f>
         <v>0</v>
       </c>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="26" t="str">
-        <f>VLOOKUP(D102,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 5708</v>
-      </c>
+      <c r="H102" s="13">
+        <v>3.9</v>
+      </c>
+      <c r="I102" s="13">
+        <v>120</v>
+      </c>
+      <c r="J102" s="26"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>3287</v>
+        <v>4993</v>
       </c>
       <c r="B103" s="48" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="C103" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D103" s="47">
-        <v>1001060763287</v>
+        <v>1001060764993</v>
       </c>
       <c r="E103" s="22"/>
       <c r="F103" s="21">
-        <v>0.48799999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G103" s="21">
-        <f t="shared" ref="G103" si="19">E103</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H103" s="13">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="I103" s="13">
         <v>120</v>
@@ -11317,16 +11316,16 @@
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>4993</v>
+        <v>5483</v>
       </c>
       <c r="B104" s="48" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="C104" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="47">
-        <v>1001060764993</v>
+        <v>1001062505483</v>
       </c>
       <c r="E104" s="22"/>
       <c r="F104" s="21">
@@ -11347,27 +11346,27 @@
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>5483</v>
+        <v>4117</v>
       </c>
       <c r="B105" s="48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C105" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D105" s="47">
-        <v>1001062505483</v>
+        <v>1001062504117</v>
       </c>
       <c r="E105" s="22"/>
       <c r="F105" s="21">
-        <v>0.25</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G105" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G105:G106" si="20">E105</f>
         <v>0</v>
       </c>
       <c r="H105" s="13">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="I105" s="13">
         <v>120</v>
@@ -11377,27 +11376,27 @@
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>4117</v>
+        <v>0614</v>
       </c>
       <c r="B106" s="48" t="s">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="C106" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D106" s="47">
-        <v>1001062504117</v>
+        <v>1001060720614</v>
       </c>
       <c r="E106" s="22"/>
       <c r="F106" s="21">
-        <v>0.49399999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="G106" s="21">
-        <f t="shared" ref="G106:G107" si="20">E106</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H106" s="13">
-        <v>3.95</v>
+        <v>3.64</v>
       </c>
       <c r="I106" s="13">
         <v>120</v>
@@ -11407,27 +11406,27 @@
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>0614</v>
+        <v>6967</v>
       </c>
       <c r="B107" s="48" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="C107" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D107" s="47">
-        <v>1001060720614</v>
+        <v>1001063656967</v>
       </c>
       <c r="E107" s="22"/>
       <c r="F107" s="21">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="G107" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G107:G115" si="21">E107*F107</f>
         <v>0</v>
       </c>
       <c r="H107" s="13">
-        <v>3.64</v>
+        <v>2</v>
       </c>
       <c r="I107" s="13">
         <v>120</v>
@@ -11437,23 +11436,23 @@
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6967</v>
+        <v>6937</v>
       </c>
       <c r="B108" s="48" t="s">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="C108" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D108" s="47">
-        <v>1001063656967</v>
+        <v>1001063106937</v>
       </c>
       <c r="E108" s="22"/>
       <c r="F108" s="21">
         <v>0.25</v>
       </c>
       <c r="G108" s="21">
-        <f t="shared" ref="G108:G116" si="21">E108*F108</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H108" s="13">
@@ -11467,27 +11466,27 @@
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6937</v>
+        <v>7143</v>
       </c>
       <c r="B109" s="48" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C109" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D109" s="47">
-        <v>1001063106937</v>
+        <v>1001060717143</v>
       </c>
       <c r="E109" s="22"/>
       <c r="F109" s="21">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G109" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H109" s="13">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="I109" s="13">
         <v>120</v>
@@ -11497,57 +11496,57 @@
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7143</v>
+        <v>7456</v>
       </c>
       <c r="B110" s="48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C110" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D110" s="47">
-        <v>1001060717143</v>
+        <v>1001063097456</v>
       </c>
       <c r="E110" s="22"/>
       <c r="F110" s="21">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G110" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H110" s="13">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I110" s="13">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J110" s="26"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7456</v>
+        <v>7364</v>
       </c>
       <c r="B111" s="48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D111" s="47">
-        <v>1001063097456</v>
+        <v>1001063217364</v>
       </c>
       <c r="E111" s="22"/>
       <c r="F111" s="21">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G111" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H111" s="13">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I111" s="13">
         <v>90</v>
@@ -11557,16 +11556,16 @@
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7364</v>
+        <v>7383</v>
       </c>
       <c r="B112" s="48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C112" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D112" s="47">
-        <v>1001063217364</v>
+        <v>1001065467383</v>
       </c>
       <c r="E112" s="22"/>
       <c r="F112" s="21">
@@ -11587,57 +11586,57 @@
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7383</v>
+        <v>7317</v>
       </c>
       <c r="B113" s="48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C113" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D113" s="47">
-        <v>1001065467383</v>
+        <v>1001066567317</v>
       </c>
       <c r="E113" s="22"/>
       <c r="F113" s="21">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="G113" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H113" s="13">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I113" s="13">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J113" s="26"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7317</v>
+        <v>7318</v>
       </c>
       <c r="B114" s="48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C114" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D114" s="47">
-        <v>1001066567317</v>
+        <v>1001060727318</v>
       </c>
       <c r="E114" s="22"/>
       <c r="F114" s="21">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G114" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H114" s="13">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I114" s="13">
         <v>120</v>
@@ -11647,27 +11646,27 @@
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7318</v>
+        <v>7316</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C115" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D115" s="47">
-        <v>1001060727318</v>
+        <v>1001060727316</v>
       </c>
       <c r="E115" s="22"/>
       <c r="F115" s="21">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G115" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H115" s="13">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I115" s="13">
         <v>120</v>
@@ -11677,53 +11676,53 @@
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7316</v>
+        <v>6832</v>
       </c>
       <c r="B116" s="48" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="C116" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D116" s="47">
-        <v>1001060727316</v>
+        <v>1001065616832</v>
       </c>
       <c r="E116" s="22"/>
       <c r="F116" s="21">
-        <v>0.54</v>
+        <v>0.215</v>
       </c>
       <c r="G116" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G116:G117" si="22">E116</f>
         <v>0</v>
       </c>
       <c r="H116" s="13">
-        <v>3.78</v>
+        <v>2.15</v>
       </c>
       <c r="I116" s="13">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="J116" s="26"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6832</v>
+        <v>7299</v>
       </c>
       <c r="B117" s="48" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C117" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D117" s="47">
-        <v>1001065616832</v>
+        <v>1001060677299</v>
       </c>
       <c r="E117" s="22"/>
       <c r="F117" s="21">
         <v>0.215</v>
       </c>
       <c r="G117" s="21">
-        <f t="shared" ref="G117:G118" si="22">E117</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H117" s="13">
@@ -11737,87 +11736,87 @@
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7299</v>
+        <v>7386</v>
       </c>
       <c r="B118" s="48" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="C118" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D118" s="47">
-        <v>1001060677299</v>
+        <v>1001067017386</v>
       </c>
       <c r="E118" s="22"/>
       <c r="F118" s="21">
-        <v>0.215</v>
+        <v>0.15</v>
       </c>
       <c r="G118" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G118:G125" si="23">E118*F118</f>
         <v>0</v>
       </c>
       <c r="H118" s="13">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="I118" s="13">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J118" s="26"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7386</v>
+        <v>7613</v>
       </c>
       <c r="B119" s="48" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="C119" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="47">
-        <v>1001067017386</v>
+        <v>1001061977613</v>
       </c>
       <c r="E119" s="22"/>
       <c r="F119" s="21">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G119" s="21">
-        <f t="shared" ref="G119:G126" si="23">E119*F119</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H119" s="13">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="I119" s="13">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J119" s="26"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7613</v>
+        <v>7382</v>
       </c>
       <c r="B120" s="48" t="s">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="C120" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="47">
-        <v>1001061977613</v>
+        <v>1001203117382</v>
       </c>
       <c r="E120" s="22"/>
       <c r="F120" s="21">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G120" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H120" s="13">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I120" s="13">
         <v>60</v>
@@ -11827,27 +11826,27 @@
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7382</v>
+        <v>7616</v>
       </c>
       <c r="B121" s="48" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="C121" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D121" s="47">
-        <v>1001203117382</v>
+        <v>1001062507616</v>
       </c>
       <c r="E121" s="22"/>
       <c r="F121" s="21">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G121" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H121" s="13">
-        <v>0.96</v>
+        <v>1.4</v>
       </c>
       <c r="I121" s="13">
         <v>60</v>
@@ -11857,27 +11856,27 @@
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7616</v>
+        <v>6221</v>
       </c>
       <c r="B122" s="48" t="s">
-        <v>198</v>
+        <v>87</v>
       </c>
       <c r="C122" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="47">
-        <v>1001062507616</v>
+        <v>1001205376221</v>
       </c>
       <c r="E122" s="22"/>
       <c r="F122" s="21">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G122" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H122" s="13">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I122" s="13">
         <v>60</v>
@@ -11887,16 +11886,16 @@
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6221</v>
+        <v>6222</v>
       </c>
       <c r="B123" s="48" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="C123" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="47">
-        <v>1001205376221</v>
+        <v>1001205386222</v>
       </c>
       <c r="E123" s="22"/>
       <c r="F123" s="21">
@@ -11917,192 +11916,192 @@
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6222</v>
+        <v>5679</v>
       </c>
       <c r="B124" s="48" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C124" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="47">
-        <v>1001205386222</v>
+        <v>1001190765679</v>
       </c>
       <c r="E124" s="22"/>
       <c r="F124" s="21">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G124" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H124" s="13">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I124" s="13">
         <v>60</v>
       </c>
       <c r="J124" s="26"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>5679</v>
+        <v>7626</v>
       </c>
       <c r="B125" s="48" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="C125" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D125" s="47">
-        <v>1001190765679</v>
+        <v>1001066607626</v>
       </c>
       <c r="E125" s="22"/>
       <c r="F125" s="21">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G125" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H125" s="13">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I125" s="13">
         <v>60</v>
       </c>
       <c r="J125" s="26"/>
     </row>
-    <row r="126" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="100" t="str">
-        <f t="shared" si="17"/>
-        <v>7626</v>
-      </c>
-      <c r="B126" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="C126" s="46" t="s">
+    <row r="126" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B126" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C126" s="39"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="39"/>
+      <c r="F126" s="38"/>
+      <c r="G126" s="39"/>
+      <c r="H126" s="39"/>
+      <c r="I126" s="39"/>
+      <c r="J126" s="40"/>
+    </row>
+    <row r="127" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="100" t="str">
+        <f t="shared" ref="A127:A138" si="24">RIGHT(D127,4)</f>
+        <v>4584</v>
+      </c>
+      <c r="B127" s="92" t="s">
+        <v>125</v>
+      </c>
+      <c r="C127" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="D127" s="107">
+        <v>1001092674584</v>
+      </c>
+      <c r="E127" s="22"/>
+      <c r="F127" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="G127" s="21">
+        <f>E127</f>
+        <v>0</v>
+      </c>
+      <c r="H127" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="I127" s="13">
+        <v>60</v>
+      </c>
+      <c r="J127" s="26"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="100" t="str">
+        <f t="shared" si="24"/>
+        <v>7725</v>
+      </c>
+      <c r="B128" s="92" t="s">
+        <v>219</v>
+      </c>
+      <c r="C128" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="D126" s="47">
-        <v>1001066607626</v>
-      </c>
-      <c r="E126" s="22"/>
-      <c r="F126" s="21">
-        <v>0.1</v>
-      </c>
-      <c r="G126" s="21">
-        <f t="shared" si="23"/>
+      <c r="D128" s="47">
+        <v>1001092437725</v>
+      </c>
+      <c r="E128" s="22"/>
+      <c r="F128" s="102">
+        <v>0.3</v>
+      </c>
+      <c r="G128" s="21">
+        <f>E128*F128</f>
         <v>0</v>
       </c>
-      <c r="H126" s="13">
-        <v>1</v>
-      </c>
-      <c r="I126" s="13">
-        <v>60</v>
-      </c>
-      <c r="J126" s="26"/>
-    </row>
-    <row r="127" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B127" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C127" s="39"/>
-      <c r="D127" s="39"/>
-      <c r="E127" s="39"/>
-      <c r="F127" s="38"/>
-      <c r="G127" s="39"/>
-      <c r="H127" s="39"/>
-      <c r="I127" s="39"/>
-      <c r="J127" s="40"/>
-    </row>
-    <row r="128" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="100" t="str">
-        <f t="shared" ref="A128:A139" si="24">RIGHT(D128,4)</f>
-        <v>4584</v>
-      </c>
-      <c r="B128" s="92" t="s">
-        <v>125</v>
-      </c>
-      <c r="C128" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="D128" s="107">
-        <v>1001092674584</v>
-      </c>
-      <c r="E128" s="22"/>
-      <c r="F128" s="21">
-        <v>2.5</v>
-      </c>
-      <c r="G128" s="21">
-        <f>E128</f>
-        <v>0</v>
-      </c>
-      <c r="H128" s="13">
-        <v>7.5</v>
-      </c>
-      <c r="I128" s="13">
-        <v>60</v>
-      </c>
-      <c r="J128" s="26"/>
+      <c r="H128" s="26"/>
+      <c r="I128" s="26"/>
+      <c r="J128" s="26" t="str">
+        <f>VLOOKUP(D128,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 6495</v>
+      </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7725</v>
-      </c>
-      <c r="B129" s="92" t="s">
-        <v>219</v>
+        <v>5452</v>
+      </c>
+      <c r="B129" s="108" t="s">
+        <v>95</v>
       </c>
       <c r="C129" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D129" s="47">
-        <v>1001092437725</v>
+        <v>1001092485452</v>
       </c>
       <c r="E129" s="22"/>
       <c r="F129" s="102">
-        <v>0.3</v>
+        <v>1.35</v>
       </c>
       <c r="G129" s="21">
-        <f>E129*F129</f>
+        <f t="shared" ref="G129" si="25">E129</f>
         <v>0</v>
       </c>
-      <c r="H129" s="26"/>
-      <c r="I129" s="26"/>
-      <c r="J129" s="26" t="str">
-        <f>VLOOKUP(D129,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 6495</v>
-      </c>
+      <c r="H129" s="26">
+        <v>4.05</v>
+      </c>
+      <c r="I129" s="26">
+        <v>60</v>
+      </c>
+      <c r="J129" s="26"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>5452</v>
+        <v>3215</v>
       </c>
       <c r="B130" s="108" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C130" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D130" s="47">
-        <v>1001092485452</v>
+        <v>1001094053215</v>
       </c>
       <c r="E130" s="22"/>
       <c r="F130" s="102">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G130" s="21">
-        <f t="shared" ref="G130" si="25">E130</f>
+        <f>E130*F130</f>
         <v>0</v>
       </c>
       <c r="H130" s="26">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I130" s="26">
         <v>60</v>
@@ -12112,27 +12111,27 @@
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>3215</v>
+        <v>6866</v>
       </c>
       <c r="B131" s="108" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C131" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D131" s="47">
-        <v>1001094053215</v>
+        <v>1001095716866</v>
       </c>
       <c r="E131" s="22"/>
       <c r="F131" s="102">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G131" s="21">
-        <f>E131*F131</f>
+        <f>E131</f>
         <v>0</v>
       </c>
       <c r="H131" s="26">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I131" s="26">
         <v>60</v>
@@ -12142,27 +12141,27 @@
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>6866</v>
-      </c>
-      <c r="B132" s="108" t="s">
-        <v>93</v>
+        <v>5495</v>
+      </c>
+      <c r="B132" s="48" t="s">
+        <v>96</v>
       </c>
       <c r="C132" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="D132" s="47">
-        <v>1001095716866</v>
+        <v>21</v>
+      </c>
+      <c r="D132" s="101">
+        <v>1001093345495</v>
       </c>
       <c r="E132" s="22"/>
       <c r="F132" s="102">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G132" s="21">
-        <f>E132</f>
+        <f t="shared" ref="G132:G133" si="26">E132*F132</f>
         <v>0</v>
       </c>
       <c r="H132" s="26">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="I132" s="26">
         <v>60</v>
@@ -12172,159 +12171,158 @@
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>5495</v>
+        <v>7377</v>
       </c>
       <c r="B133" s="48" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="C133" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D133" s="101">
-        <v>1001093345495</v>
+        <v>1001095027377</v>
       </c>
       <c r="E133" s="22"/>
       <c r="F133" s="102">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G133" s="21">
-        <f t="shared" ref="G133:G134" si="26">E133*F133</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H133" s="26">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="I133" s="26">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J133" s="26"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7377</v>
+        <v>6025</v>
       </c>
       <c r="B134" s="48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C134" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D134" s="101">
-        <v>1001095027377</v>
+        <v>1001094966025</v>
       </c>
       <c r="E134" s="22"/>
       <c r="F134" s="102">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="G134" s="21">
-        <f t="shared" si="26"/>
+        <f>E134</f>
         <v>0</v>
       </c>
       <c r="H134" s="26">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="I134" s="26">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J134" s="26"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>6025</v>
+        <v>6929</v>
       </c>
       <c r="B135" s="48" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="C135" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D135" s="101">
-        <v>1001094966025</v>
+        <v>1001085476929</v>
       </c>
       <c r="E135" s="22"/>
-      <c r="F135" s="102">
-        <v>3</v>
-      </c>
+      <c r="F135" s="102"/>
       <c r="G135" s="21">
         <f>E135</f>
         <v>0</v>
       </c>
-      <c r="H135" s="26">
-        <v>6</v>
-      </c>
-      <c r="I135" s="26">
-        <v>60</v>
-      </c>
-      <c r="J135" s="26"/>
+      <c r="H135" s="26"/>
+      <c r="I135" s="26"/>
+      <c r="J135" s="26" t="str">
+        <f>VLOOKUP(D135,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>6929</v>
+        <v>7485</v>
       </c>
       <c r="B136" s="48" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C136" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D136" s="101">
-        <v>1001085476929</v>
+        <v>1001107397485</v>
       </c>
       <c r="E136" s="22"/>
-      <c r="F136" s="102"/>
+      <c r="F136" s="102">
+        <v>0.15</v>
+      </c>
       <c r="G136" s="21">
-        <f>E136</f>
+        <f>F136*E136</f>
         <v>0</v>
       </c>
       <c r="H136" s="26"/>
       <c r="I136" s="26"/>
-      <c r="J136" s="26" t="str">
-        <f>VLOOKUP(D136,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="J136" s="26"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7485</v>
+        <v>7730</v>
       </c>
       <c r="B137" s="48" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C137" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="101">
-        <v>1001107397485</v>
+        <v>1001097747730</v>
       </c>
       <c r="E137" s="22"/>
       <c r="F137" s="102">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G137" s="21">
-        <f>F137*E137</f>
+        <f>E137*F137</f>
         <v>0</v>
       </c>
       <c r="H137" s="26"/>
       <c r="I137" s="26"/>
-      <c r="J137" s="26"/>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J137" s="26" t="str">
+        <f>VLOOKUP(D137,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 7647</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7730</v>
+        <v>7731</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C138" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="101">
-        <v>1001097747730</v>
+        <v>1001097767731</v>
       </c>
       <c r="E138" s="22"/>
       <c r="F138" s="102">
@@ -12334,82 +12332,83 @@
         <f>E138*F138</f>
         <v>0</v>
       </c>
-      <c r="H138" s="26"/>
-      <c r="I138" s="26"/>
+      <c r="H138" s="26">
+        <v>1</v>
+      </c>
+      <c r="I138" s="26">
+        <v>30</v>
+      </c>
       <c r="J138" s="26" t="str">
         <f>VLOOKUP(D138,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 7647</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="100" t="str">
-        <f t="shared" si="24"/>
-        <v>7731</v>
-      </c>
-      <c r="B139" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="C139" s="46" t="s">
+        <v>Ротация кода 7651</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B139" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C139" s="39"/>
+      <c r="D139" s="39"/>
+      <c r="E139" s="39"/>
+      <c r="F139" s="38"/>
+      <c r="G139" s="39"/>
+      <c r="H139" s="39"/>
+      <c r="I139" s="39"/>
+      <c r="J139" s="40"/>
+    </row>
+    <row r="140" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="100" t="str">
+        <f t="shared" ref="A140:A152" si="27">RIGHT(D140,4)</f>
+        <v>7090</v>
+      </c>
+      <c r="B140" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C140" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="D139" s="101">
-        <v>1001097767731</v>
-      </c>
-      <c r="E139" s="22"/>
-      <c r="F139" s="102">
-        <v>0.1</v>
-      </c>
-      <c r="G139" s="21">
-        <f>E139*F139</f>
+      <c r="D140" s="47">
+        <v>1001084217090</v>
+      </c>
+      <c r="E140" s="22"/>
+      <c r="F140" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="G140" s="21">
+        <f t="shared" ref="G140:G141" si="28">E140*F140</f>
         <v>0</v>
       </c>
-      <c r="H139" s="26">
-        <v>1</v>
-      </c>
-      <c r="I139" s="26">
-        <v>30</v>
-      </c>
-      <c r="J139" s="26" t="str">
-        <f>VLOOKUP(D139,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 7651</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B140" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C140" s="39"/>
-      <c r="D140" s="39"/>
-      <c r="E140" s="39"/>
-      <c r="F140" s="38"/>
-      <c r="G140" s="39"/>
-      <c r="H140" s="39"/>
-      <c r="I140" s="39"/>
-      <c r="J140" s="40"/>
-    </row>
-    <row r="141" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H140" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="I140" s="13">
+        <v>50</v>
+      </c>
+      <c r="J140" s="26"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="100" t="str">
-        <f t="shared" ref="A141:A153" si="27">RIGHT(D141,4)</f>
-        <v>7090</v>
+        <f t="shared" si="27"/>
+        <v>7187</v>
       </c>
       <c r="B141" s="32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C141" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D141" s="47">
-        <v>1001084217090</v>
+        <v>1001085637187</v>
       </c>
       <c r="E141" s="22"/>
       <c r="F141" s="21">
         <v>0.3</v>
       </c>
       <c r="G141" s="21">
-        <f t="shared" ref="G141:G142" si="28">E141*F141</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H141" s="13">
@@ -12423,117 +12422,117 @@
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7187</v>
+        <v>6008</v>
       </c>
       <c r="B142" s="32" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="C142" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D142" s="47">
-        <v>1001085637187</v>
+        <v>1001084856008</v>
       </c>
       <c r="E142" s="22"/>
       <c r="F142" s="21">
         <v>0.3</v>
       </c>
       <c r="G142" s="21">
-        <f t="shared" si="28"/>
+        <f>E142</f>
         <v>0</v>
       </c>
       <c r="H142" s="13">
         <v>1.8</v>
       </c>
       <c r="I142" s="13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J142" s="26"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6008</v>
+        <v>6620</v>
       </c>
       <c r="B143" s="32" t="s">
-        <v>196</v>
+        <v>99</v>
       </c>
       <c r="C143" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D143" s="47">
-        <v>1001084856008</v>
+        <v>1001081596620</v>
       </c>
       <c r="E143" s="22"/>
       <c r="F143" s="21">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="G143" s="21">
         <f>E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="13">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I143" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J143" s="26"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6620</v>
+        <v>7103</v>
       </c>
       <c r="B144" s="32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C144" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D144" s="47">
-        <v>1001081596620</v>
+        <v>1001223297103</v>
       </c>
       <c r="E144" s="22"/>
       <c r="F144" s="21">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="G144" s="21">
-        <f>E144</f>
+        <f t="shared" ref="G144:G151" si="29">E144*F144</f>
         <v>0</v>
       </c>
       <c r="H144" s="13">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I144" s="13">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J144" s="26"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7103</v>
+        <v>7092</v>
       </c>
       <c r="B145" s="32" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="C145" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D145" s="47">
-        <v>1001223297103</v>
+        <v>1001223297092</v>
       </c>
       <c r="E145" s="22"/>
       <c r="F145" s="21">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G145" s="21">
-        <f t="shared" ref="G145:G152" si="29">E145*F145</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H145" s="13">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="I145" s="13">
         <v>50</v>
@@ -12543,57 +12542,57 @@
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7092</v>
+        <v>6228</v>
       </c>
       <c r="B146" s="32" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C146" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D146" s="47">
-        <v>1001223297092</v>
+        <v>1001225416228</v>
       </c>
       <c r="E146" s="22"/>
       <c r="F146" s="21">
-        <v>0.14000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G146" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H146" s="13">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I146" s="13">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J146" s="26"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6228</v>
+        <v>6208</v>
       </c>
       <c r="B147" s="32" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C147" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D147" s="47">
-        <v>1001225416228</v>
+        <v>1001220226208</v>
       </c>
       <c r="E147" s="22"/>
       <c r="F147" s="21">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G147" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H147" s="13">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I147" s="13">
         <v>45</v>
@@ -12603,143 +12602,142 @@
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6208</v>
+        <v>6754</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="C148" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="47">
-        <v>1001220226208</v>
+        <v>1001225406754</v>
       </c>
       <c r="E148" s="22"/>
       <c r="F148" s="21">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G148" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H148" s="13">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="I148" s="13">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J148" s="26"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6754</v>
+        <v>6279</v>
       </c>
       <c r="B149" s="32" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="C149" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="47">
-        <v>1001225406754</v>
+        <v>1001220286279</v>
       </c>
       <c r="E149" s="22"/>
       <c r="F149" s="21">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G149" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H149" s="13">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="I149" s="13">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J149" s="26"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6279</v>
+        <v>7612</v>
       </c>
       <c r="B150" s="32" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="C150" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D150" s="47">
-        <v>1001220286279</v>
+        <v>1001453907612</v>
       </c>
       <c r="E150" s="22"/>
       <c r="F150" s="21">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G150" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H150" s="13">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I150" s="13">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J150" s="26"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7612</v>
+        <v>7344</v>
       </c>
       <c r="B151" s="32" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="C151" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D151" s="47">
-        <v>1001453907612</v>
+        <v>1001122287344</v>
       </c>
       <c r="E151" s="22"/>
       <c r="F151" s="21">
-        <v>0.1</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="G151" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H151" s="13">
-        <v>1</v>
-      </c>
-      <c r="I151" s="13">
-        <v>60</v>
-      </c>
-      <c r="J151" s="26"/>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H151" s="13"/>
+      <c r="I151" s="13"/>
+      <c r="J151" s="26" t="str">
+        <f>VLOOKUP(D151,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7344</v>
+        <v>7345</v>
       </c>
       <c r="B152" s="32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C152" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D152" s="47">
-        <v>1001122287344</v>
+        <v>1001123677345</v>
       </c>
       <c r="E152" s="22"/>
       <c r="F152" s="21">
-        <v>0.33800000000000002</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="G152" s="21">
-        <f t="shared" si="29"/>
+        <f>E152*F152</f>
         <v>0</v>
       </c>
       <c r="H152" s="13"/>
@@ -12749,56 +12747,37 @@
         <v>Новинка</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="100" t="str">
-        <f t="shared" si="27"/>
-        <v>7345</v>
-      </c>
-      <c r="B153" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="C153" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="D153" s="47">
-        <v>1001123677345</v>
-      </c>
-      <c r="E153" s="22"/>
-      <c r="F153" s="21">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="G153" s="21">
-        <f>E153*F153</f>
+    <row r="153" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="45"/>
+      <c r="B153" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C153" s="14"/>
+      <c r="D153" s="33"/>
+      <c r="E153" s="15">
+        <f>SUM(E10:E150)</f>
         <v>0</v>
       </c>
-      <c r="H153" s="13"/>
-      <c r="I153" s="13"/>
-      <c r="J153" s="26" t="str">
-        <f>VLOOKUP(D153,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="45"/>
-      <c r="B154" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C154" s="14"/>
-      <c r="D154" s="33"/>
-      <c r="E154" s="15">
-        <f>SUM(E10:E151)</f>
+      <c r="F153" s="15"/>
+      <c r="G153" s="15">
+        <f>SUM(G11:G152)</f>
         <v>0</v>
       </c>
-      <c r="F154" s="15"/>
-      <c r="G154" s="15">
-        <f>SUM(G11:G153)</f>
-        <v>0</v>
-      </c>
-      <c r="H154" s="15"/>
-      <c r="I154" s="15"/>
-      <c r="J154" s="15"/>
-    </row>
-    <row r="155" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H153" s="15"/>
+      <c r="I153" s="15"/>
+      <c r="J153" s="15"/>
+    </row>
+    <row r="154" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="34"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="37"/>
+      <c r="F154" s="17"/>
+      <c r="G154" s="17"/>
+      <c r="H154" s="18"/>
+      <c r="I154" s="18"/>
+      <c r="J154" s="19"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B155" s="34"/>
       <c r="C155" s="16"/>
       <c r="D155" s="37"/>
@@ -26277,16 +26256,6 @@
       <c r="H1502" s="18"/>
       <c r="I1502" s="18"/>
       <c r="J1502" s="19"/>
-    </row>
-    <row r="1503" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B1503" s="34"/>
-      <c r="C1503" s="16"/>
-      <c r="D1503" s="37"/>
-      <c r="F1503" s="17"/>
-      <c r="G1503" s="17"/>
-      <c r="H1503" s="18"/>
-      <c r="I1503" s="18"/>
-      <c r="J1503" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8660D8EB-CA39-4CA5-B4A6-A42F458628BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACE67BB-EE8C-4709-B3F0-1C081142A4C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1141,10 +1141,6 @@
     <t>КОНСЕРВЫ МЯС.СВИНИНА ТУШ. В/С 325г_ЧЗ</t>
   </si>
   <si>
-    <t xml:space="preserve">130439104 ООО "НОВОЕ ВРЕМЯ"  Мариуполь
-</t>
-  </si>
-  <si>
     <t>СОЧНЫЙ ГРИЛЬ сос ц/о мгс 0.41кг_Даблпак</t>
   </si>
   <si>
@@ -1161,6 +1157,10 @@
   </si>
   <si>
     <t>ДОМАШНИЙ РЕЦЕПТ Коровино вар п/о_332к</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130439502 ООО "НОВОЕ ВРЕМЯ"  Мариуполь
+</t>
   </si>
 </sst>
 </file>
@@ -8510,10 +8510,10 @@
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="K4" s="96">
-        <v>130439104</v>
+        <v>130439502</v>
       </c>
       <c r="L4" s="93" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -8736,7 +8736,7 @@
         <v>7754</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>23</v>
@@ -10058,7 +10058,7 @@
         <v>7490</v>
       </c>
       <c r="B60" s="48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C60" s="46" t="s">
         <v>21</v>
@@ -11232,7 +11232,7 @@
         <v>7700</v>
       </c>
       <c r="B101" s="48" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C101" s="46" t="s">
         <v>23</v>
@@ -12025,7 +12025,7 @@
         <v>7725</v>
       </c>
       <c r="B128" s="92" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C128" s="46" t="s">
         <v>21</v>
@@ -12287,7 +12287,7 @@
         <v>7730</v>
       </c>
       <c r="B137" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C137" s="46" t="s">
         <v>21</v>
@@ -12316,7 +12316,7 @@
         <v>7731</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C138" s="46" t="s">
         <v>21</v>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACE67BB-EE8C-4709-B3F0-1C081142A4C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4315AA7-7C00-4BCE-A27A-2EA65C6EA1BD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,7 +491,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="224">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1161,6 +1161,9 @@
   <si>
     <t xml:space="preserve">130439502 ООО "НОВОЕ ВРЕМЯ"  Мариуполь
 </t>
+  </si>
+  <si>
+    <t>САЛЯМИ ZHAZIRA ASLAM в/к в/у 0.82кг</t>
   </si>
 </sst>
 </file>
@@ -10415,7 +10418,7 @@
     </row>
     <row r="73" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A73" s="100" t="str">
-        <f t="shared" ref="A73:A97" si="14">RIGHT(D73,4)</f>
+        <f t="shared" ref="A73:A98" si="14">RIGHT(D73,4)</f>
         <v>7564</v>
       </c>
       <c r="B73" s="48" t="s">
@@ -10462,7 +10465,7 @@
         <v>0.33</v>
       </c>
       <c r="G74" s="21">
-        <f t="shared" ref="G74:G86" si="15">E74*F74</f>
+        <f t="shared" ref="G74:G87" si="15">E74*F74</f>
         <v>0</v>
       </c>
       <c r="H74" s="13">
@@ -10476,106 +10479,102 @@
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7149</v>
+        <v>7399</v>
       </c>
       <c r="B75" s="48" t="s">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="C75" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D75" s="47">
-        <v>1001303637149</v>
+        <v>1001057037399</v>
       </c>
       <c r="E75" s="22"/>
       <c r="F75" s="21">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="G75" s="21">
-        <f t="shared" si="15"/>
+        <f>E75*F75</f>
         <v>0</v>
       </c>
-      <c r="H75" s="13">
-        <v>5.04</v>
-      </c>
-      <c r="I75" s="13">
-        <v>50</v>
-      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
       <c r="J75" s="26"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7233</v>
+        <v>7149</v>
       </c>
       <c r="B76" s="48" t="s">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="C76" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D76" s="47">
-        <v>1001303637233</v>
+        <v>1001303637149</v>
       </c>
       <c r="E76" s="22"/>
-      <c r="F76" s="102">
-        <v>0.31</v>
+      <c r="F76" s="21">
+        <v>0.84</v>
       </c>
       <c r="G76" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H76" s="26">
-        <v>2.48</v>
-      </c>
-      <c r="I76" s="26">
-        <v>45</v>
+      <c r="H76" s="13">
+        <v>5.04</v>
+      </c>
+      <c r="I76" s="13">
+        <v>50</v>
       </c>
       <c r="J76" s="26"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7232</v>
+        <v>7233</v>
       </c>
       <c r="B77" s="48" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C77" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D77" s="47">
-        <v>1001302277232</v>
+        <v>1001303637233</v>
       </c>
       <c r="E77" s="22"/>
       <c r="F77" s="102">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G77" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H77" s="26">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I77" s="26">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J77" s="26"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7241</v>
+        <v>7232</v>
       </c>
       <c r="B78" s="48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C78" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D78" s="47">
-        <v>1001303107241</v>
+        <v>1001302277232</v>
       </c>
       <c r="E78" s="22"/>
       <c r="F78" s="102">
@@ -10589,34 +10588,34 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I78" s="26">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J78" s="26"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7133</v>
+        <v>7241</v>
       </c>
       <c r="B79" s="48" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D79" s="47">
-        <v>1001300367133</v>
+        <v>1001303107241</v>
       </c>
       <c r="E79" s="22"/>
       <c r="F79" s="102">
-        <v>0.84</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G79" s="21">
-        <f>E79</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H79" s="26">
-        <v>5.04</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I79" s="26">
         <v>45</v>
@@ -10626,111 +10625,111 @@
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6946</v>
+        <v>7133</v>
       </c>
       <c r="B80" s="48" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="C80" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D80" s="47">
-        <v>1001300456946</v>
+        <v>1001300367133</v>
       </c>
       <c r="E80" s="22"/>
-      <c r="F80" s="102"/>
+      <c r="F80" s="102">
+        <v>0.84</v>
+      </c>
       <c r="G80" s="21">
         <f>E80</f>
         <v>0</v>
       </c>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
+      <c r="H80" s="26">
+        <v>5.04</v>
+      </c>
+      <c r="I80" s="26">
+        <v>45</v>
+      </c>
       <c r="J80" s="26"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6807</v>
+        <v>6946</v>
       </c>
       <c r="B81" s="48" t="s">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="C81" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D81" s="47">
-        <v>1001300366807</v>
+        <v>1001300456946</v>
       </c>
       <c r="E81" s="22"/>
-      <c r="F81" s="102">
-        <v>0.33</v>
-      </c>
+      <c r="F81" s="102"/>
       <c r="G81" s="21">
-        <f t="shared" si="15"/>
+        <f>E81</f>
         <v>0</v>
       </c>
-      <c r="H81" s="26">
-        <v>2.64</v>
-      </c>
-      <c r="I81" s="26">
-        <v>45</v>
-      </c>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
       <c r="J81" s="26"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7154</v>
+        <v>6807</v>
       </c>
       <c r="B82" s="48" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C82" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="47">
-        <v>1001300387154</v>
+        <v>1001300366807</v>
       </c>
       <c r="E82" s="22"/>
-      <c r="F82" s="21">
-        <v>0.35</v>
+      <c r="F82" s="102">
+        <v>0.33</v>
       </c>
       <c r="G82" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H82" s="13">
-        <v>2.8</v>
-      </c>
-      <c r="I82" s="13">
-        <v>50</v>
+      <c r="H82" s="26">
+        <v>2.64</v>
+      </c>
+      <c r="I82" s="26">
+        <v>45</v>
       </c>
       <c r="J82" s="26"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7157</v>
+        <v>7154</v>
       </c>
       <c r="B83" s="48" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C83" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D83" s="47">
-        <v>1001300387157</v>
+        <v>1001300387154</v>
       </c>
       <c r="E83" s="22"/>
       <c r="F83" s="21">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="G83" s="21">
-        <f>E83</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H83" s="13">
-        <v>5.04</v>
+        <v>2.8</v>
       </c>
       <c r="I83" s="13">
         <v>50</v>
@@ -10740,84 +10739,84 @@
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7562</v>
+        <v>7157</v>
       </c>
       <c r="B84" s="48" t="s">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="C84" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D84" s="47">
-        <v>1001307587562</v>
+        <v>1001300387157</v>
       </c>
       <c r="E84" s="22"/>
-      <c r="F84" s="21"/>
+      <c r="F84" s="21">
+        <v>0.63</v>
+      </c>
       <c r="G84" s="21">
         <f>E84</f>
         <v>0</v>
       </c>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="26" t="str">
-        <f>VLOOKUP(D84,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H84" s="13">
+        <v>5.04</v>
+      </c>
+      <c r="I84" s="13">
+        <v>50</v>
+      </c>
+      <c r="J84" s="26"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7236</v>
+        <v>7562</v>
       </c>
       <c r="B85" s="48" t="s">
-        <v>69</v>
+        <v>212</v>
       </c>
       <c r="C85" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D85" s="47">
-        <v>1001304507236</v>
+        <v>1001307587562</v>
       </c>
       <c r="E85" s="22"/>
-      <c r="F85" s="21">
-        <v>0.28000000000000003</v>
-      </c>
+      <c r="F85" s="21"/>
       <c r="G85" s="21">
-        <f t="shared" si="15"/>
+        <f>E85</f>
         <v>0</v>
       </c>
-      <c r="H85" s="13">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I85" s="13">
-        <v>45</v>
-      </c>
-      <c r="J85" s="26"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="26" t="str">
+        <f>VLOOKUP(D85,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6787</v>
-      </c>
-      <c r="B86" s="104" t="s">
-        <v>66</v>
+        <v>7236</v>
+      </c>
+      <c r="B86" s="48" t="s">
+        <v>69</v>
       </c>
       <c r="C86" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D86" s="47">
-        <v>1001300456787</v>
+        <v>1001304507236</v>
       </c>
       <c r="E86" s="22"/>
       <c r="F86" s="21">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G86" s="21">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H86" s="13">
-        <v>2.64</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I86" s="13">
         <v>45</v>
@@ -10827,57 +10826,57 @@
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7166</v>
+        <v>6787</v>
       </c>
       <c r="B87" s="104" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C87" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D87" s="47">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E87" s="22"/>
       <c r="F87" s="21">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G87" s="21">
-        <f>E87</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H87" s="13">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I87" s="13">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J87" s="26"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7169</v>
-      </c>
-      <c r="B88" s="48" t="s">
-        <v>71</v>
+        <v>7166</v>
+      </c>
+      <c r="B88" s="104" t="s">
+        <v>72</v>
       </c>
       <c r="C88" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D88" s="47">
-        <v>1001303987169</v>
+        <v>1001303987166</v>
       </c>
       <c r="E88" s="22"/>
       <c r="F88" s="21">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G88" s="21">
-        <f>E88*F88</f>
+        <f>E88</f>
         <v>0</v>
       </c>
       <c r="H88" s="13">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I88" s="13">
         <v>50</v>
@@ -10887,16 +10886,16 @@
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7156</v>
+        <v>7169</v>
       </c>
       <c r="B89" s="48" t="s">
-        <v>208</v>
+        <v>71</v>
       </c>
       <c r="C89" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D89" s="47">
-        <v>1001304237156</v>
+        <v>1001303987169</v>
       </c>
       <c r="E89" s="22"/>
       <c r="F89" s="21">
@@ -10906,67 +10905,67 @@
         <f>E89*F89</f>
         <v>0</v>
       </c>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="26" t="str">
-        <f>VLOOKUP(D89,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H89" s="13">
+        <v>2.8</v>
+      </c>
+      <c r="I89" s="13">
+        <v>50</v>
+      </c>
+      <c r="J89" s="26"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>5544</v>
+        <v>7156</v>
       </c>
       <c r="B90" s="48" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="C90" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D90" s="47">
-        <v>1001051875544</v>
+        <v>1001304237156</v>
       </c>
       <c r="E90" s="22"/>
       <c r="F90" s="21">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G90" s="21">
-        <f>E90</f>
+        <f>E90*F90</f>
         <v>0</v>
       </c>
-      <c r="H90" s="13">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="I90" s="13">
-        <v>45</v>
-      </c>
-      <c r="J90" s="26"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="26" t="str">
+        <f>VLOOKUP(D90,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>6697</v>
+        <v>5544</v>
       </c>
       <c r="B91" s="48" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C91" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D91" s="47">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E91" s="22"/>
       <c r="F91" s="21">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G91" s="21">
-        <f t="shared" ref="G91:G97" si="16">E91*F91</f>
+        <f>E91</f>
         <v>0</v>
       </c>
       <c r="H91" s="13">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I91" s="13">
         <v>45</v>
@@ -10976,27 +10975,27 @@
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7238</v>
+        <v>6697</v>
       </c>
       <c r="B92" s="48" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="C92" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="47">
-        <v>1001305197238</v>
+        <v>1001301876697</v>
       </c>
       <c r="E92" s="22"/>
       <c r="F92" s="21">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G92" s="21">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G92:G98" si="16">E92*F92</f>
         <v>0</v>
       </c>
       <c r="H92" s="13">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I92" s="13">
         <v>45</v>
@@ -11006,16 +11005,16 @@
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7516</v>
+        <v>7238</v>
       </c>
       <c r="B93" s="48" t="s">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="C93" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D93" s="47">
-        <v>1001307107516</v>
+        <v>1001305197238</v>
       </c>
       <c r="E93" s="22"/>
       <c r="F93" s="21">
@@ -11025,30 +11024,31 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="26" t="str">
-        <f>VLOOKUP(D93,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H93" s="13">
+        <v>2.48</v>
+      </c>
+      <c r="I93" s="13">
+        <v>45</v>
+      </c>
+      <c r="J93" s="26"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7710</v>
+        <v>7516</v>
       </c>
       <c r="B94" s="48" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C94" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D94" s="47">
-        <v>1001307587710</v>
+        <v>1001307107516</v>
       </c>
       <c r="E94" s="22"/>
       <c r="F94" s="21">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="G94" s="21">
         <f t="shared" si="16"/>
@@ -11064,20 +11064,20 @@
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7710</v>
       </c>
       <c r="B95" s="48" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C95" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D95" s="47">
-        <v>1001307077513</v>
+        <v>1001307587710</v>
       </c>
       <c r="E95" s="22"/>
       <c r="F95" s="21">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="G95" s="21">
         <f t="shared" si="16"/>
@@ -11093,135 +11093,134 @@
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7177</v>
+        <v>7513</v>
       </c>
       <c r="B96" s="48" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="C96" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D96" s="47">
-        <v>1001302347177</v>
+        <v>1001307077513</v>
       </c>
       <c r="E96" s="22"/>
       <c r="F96" s="21">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="G96" s="21">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H96" s="13">
-        <v>2.8</v>
-      </c>
-      <c r="I96" s="13">
-        <v>50</v>
-      </c>
-      <c r="J96" s="26"/>
-    </row>
-    <row r="97" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H96" s="13"/>
+      <c r="I96" s="13"/>
+      <c r="J96" s="26" t="str">
+        <f>VLOOKUP(D96,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="100" t="str">
         <f t="shared" si="14"/>
-        <v>7608</v>
+        <v>7177</v>
       </c>
       <c r="B97" s="48" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="C97" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D97" s="47">
-        <v>1001304197608</v>
+        <v>1001302347177</v>
       </c>
       <c r="E97" s="22"/>
       <c r="F97" s="21">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="21">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H97" s="13">
+        <v>2.8</v>
+      </c>
+      <c r="I97" s="13">
+        <v>50</v>
+      </c>
+      <c r="J97" s="26"/>
+    </row>
+    <row r="98" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="100" t="str">
+        <f t="shared" si="14"/>
+        <v>7608</v>
+      </c>
+      <c r="B98" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="C98" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="47">
+        <v>1001304197608</v>
+      </c>
+      <c r="E98" s="22"/>
+      <c r="F98" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="G98" s="21">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="13">
         <v>1</v>
       </c>
-      <c r="I97" s="13">
+      <c r="I98" s="13">
         <v>45</v>
       </c>
-      <c r="J97" s="26"/>
-    </row>
-    <row r="98" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="44" t="s">
+      <c r="J98" s="26"/>
+    </row>
+    <row r="99" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="B98" s="39" t="s">
+      <c r="B99" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="39"/>
-      <c r="J98" s="40"/>
-    </row>
-    <row r="99" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="100" t="str">
-        <f t="shared" ref="A99:A125" si="17">RIGHT(D99,4)</f>
+      <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="39"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="39"/>
+      <c r="H99" s="39"/>
+      <c r="I99" s="39"/>
+      <c r="J99" s="40"/>
+    </row>
+    <row r="100" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="100" t="str">
+        <f t="shared" ref="A100:A126" si="17">RIGHT(D100,4)</f>
         <v>3986</v>
       </c>
-      <c r="B99" s="48" t="s">
+      <c r="B100" s="48" t="s">
         <v>80</v>
-      </c>
-      <c r="C99" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" s="47">
-        <v>1001061973986</v>
-      </c>
-      <c r="E99" s="22"/>
-      <c r="F99" s="102">
-        <v>0.25</v>
-      </c>
-      <c r="G99" s="21">
-        <f t="shared" ref="G99:G104" si="18">E99*F99</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="105">
-        <v>2</v>
-      </c>
-      <c r="I99" s="106">
-        <v>120</v>
-      </c>
-      <c r="J99" s="26"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="100" t="str">
-        <f t="shared" si="17"/>
-        <v>5931</v>
-      </c>
-      <c r="B100" s="48" t="s">
-        <v>78</v>
       </c>
       <c r="C100" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D100" s="47">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E100" s="22"/>
-      <c r="F100" s="21">
-        <v>0.22</v>
+      <c r="F100" s="102">
+        <v>0.25</v>
       </c>
       <c r="G100" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G100:G105" si="18">E100*F100</f>
         <v>0</v>
       </c>
-      <c r="H100" s="91">
-        <v>1.76</v>
-      </c>
-      <c r="I100" s="13">
+      <c r="H100" s="105">
+        <v>2</v>
+      </c>
+      <c r="I100" s="106">
         <v>120</v>
       </c>
       <c r="J100" s="26"/>
@@ -11229,84 +11228,84 @@
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7700</v>
+        <v>5931</v>
       </c>
       <c r="B101" s="48" t="s">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="C101" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D101" s="47">
-        <v>1001067977700</v>
+        <v>1001060755931</v>
       </c>
       <c r="E101" s="22"/>
-      <c r="F101" s="21"/>
+      <c r="F101" s="21">
+        <v>0.22</v>
+      </c>
       <c r="G101" s="21">
-        <f>E101</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="26" t="str">
-        <f>VLOOKUP(D101,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 5708</v>
-      </c>
+      <c r="H101" s="91">
+        <v>1.76</v>
+      </c>
+      <c r="I101" s="13">
+        <v>120</v>
+      </c>
+      <c r="J101" s="26"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>3287</v>
+        <v>7700</v>
       </c>
       <c r="B102" s="48" t="s">
-        <v>91</v>
+        <v>217</v>
       </c>
       <c r="C102" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D102" s="47">
-        <v>1001060763287</v>
+        <v>1001067977700</v>
       </c>
       <c r="E102" s="22"/>
-      <c r="F102" s="21">
-        <v>0.48799999999999999</v>
-      </c>
+      <c r="F102" s="21"/>
       <c r="G102" s="21">
-        <f t="shared" ref="G102" si="19">E102</f>
+        <f>E102</f>
         <v>0</v>
       </c>
-      <c r="H102" s="13">
-        <v>3.9</v>
-      </c>
-      <c r="I102" s="13">
-        <v>120</v>
-      </c>
-      <c r="J102" s="26"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="26" t="str">
+        <f>VLOOKUP(D102,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 5708</v>
+      </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>4993</v>
+        <v>3287</v>
       </c>
       <c r="B103" s="48" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="C103" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D103" s="47">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E103" s="22"/>
       <c r="F103" s="21">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G103" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G103" si="19">E103</f>
         <v>0</v>
       </c>
       <c r="H103" s="13">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I103" s="13">
         <v>120</v>
@@ -11316,16 +11315,16 @@
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>5483</v>
+        <v>4993</v>
       </c>
       <c r="B104" s="48" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="C104" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D104" s="47">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E104" s="22"/>
       <c r="F104" s="21">
@@ -11346,27 +11345,27 @@
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>4117</v>
+        <v>5483</v>
       </c>
       <c r="B105" s="48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C105" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D105" s="47">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E105" s="22"/>
       <c r="F105" s="21">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G105" s="21">
-        <f t="shared" ref="G105:G106" si="20">E105</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H105" s="13">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I105" s="13">
         <v>120</v>
@@ -11376,27 +11375,27 @@
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>0614</v>
+        <v>4117</v>
       </c>
       <c r="B106" s="48" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="C106" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D106" s="47">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E106" s="22"/>
       <c r="F106" s="21">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G106" s="21">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G106:G107" si="20">E106</f>
         <v>0</v>
       </c>
       <c r="H106" s="13">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I106" s="13">
         <v>120</v>
@@ -11406,27 +11405,27 @@
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6967</v>
+        <v>0614</v>
       </c>
       <c r="B107" s="48" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="C107" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D107" s="47">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E107" s="22"/>
       <c r="F107" s="21">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G107" s="21">
-        <f t="shared" ref="G107:G115" si="21">E107*F107</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H107" s="13">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I107" s="13">
         <v>120</v>
@@ -11436,23 +11435,23 @@
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6937</v>
+        <v>6967</v>
       </c>
       <c r="B108" s="48" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C108" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D108" s="47">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E108" s="22"/>
       <c r="F108" s="21">
         <v>0.25</v>
       </c>
       <c r="G108" s="21">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G108:G116" si="21">E108*F108</f>
         <v>0</v>
       </c>
       <c r="H108" s="13">
@@ -11466,27 +11465,27 @@
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7143</v>
+        <v>6937</v>
       </c>
       <c r="B109" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C109" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D109" s="47">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E109" s="22"/>
       <c r="F109" s="21">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G109" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H109" s="13">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I109" s="13">
         <v>120</v>
@@ -11496,57 +11495,57 @@
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7456</v>
+        <v>7143</v>
       </c>
       <c r="B110" s="48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C110" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D110" s="47">
-        <v>1001063097456</v>
+        <v>1001060717143</v>
       </c>
       <c r="E110" s="22"/>
       <c r="F110" s="21">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G110" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H110" s="13">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I110" s="13">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J110" s="26"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7364</v>
+        <v>7456</v>
       </c>
       <c r="B111" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D111" s="47">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E111" s="22"/>
       <c r="F111" s="21">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G111" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H111" s="13">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I111" s="13">
         <v>90</v>
@@ -11556,16 +11555,16 @@
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7383</v>
+        <v>7364</v>
       </c>
       <c r="B112" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C112" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D112" s="47">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E112" s="22"/>
       <c r="F112" s="21">
@@ -11586,57 +11585,57 @@
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7317</v>
+        <v>7383</v>
       </c>
       <c r="B113" s="48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C113" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D113" s="47">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E113" s="22"/>
       <c r="F113" s="21">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G113" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H113" s="13">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I113" s="13">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J113" s="26"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7318</v>
+        <v>7317</v>
       </c>
       <c r="B114" s="48" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C114" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D114" s="47">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E114" s="22"/>
       <c r="F114" s="21">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G114" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H114" s="13">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I114" s="13">
         <v>120</v>
@@ -11646,27 +11645,27 @@
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7316</v>
+        <v>7318</v>
       </c>
       <c r="B115" s="48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C115" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D115" s="47">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E115" s="22"/>
       <c r="F115" s="21">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G115" s="21">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H115" s="13">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I115" s="13">
         <v>120</v>
@@ -11676,53 +11675,53 @@
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6832</v>
+        <v>7316</v>
       </c>
       <c r="B116" s="48" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="C116" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D116" s="47">
-        <v>1001065616832</v>
+        <v>1001060727316</v>
       </c>
       <c r="E116" s="22"/>
       <c r="F116" s="21">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G116" s="21">
-        <f t="shared" ref="G116:G117" si="22">E116</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H116" s="13">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I116" s="13">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J116" s="26"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7299</v>
+        <v>6832</v>
       </c>
       <c r="B117" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C117" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D117" s="47">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E117" s="22"/>
       <c r="F117" s="21">
         <v>0.215</v>
       </c>
       <c r="G117" s="21">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G117:G118" si="22">E117</f>
         <v>0</v>
       </c>
       <c r="H117" s="13">
@@ -11736,87 +11735,87 @@
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7386</v>
+        <v>7299</v>
       </c>
       <c r="B118" s="48" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="C118" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D118" s="47">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E118" s="22"/>
       <c r="F118" s="21">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G118" s="21">
-        <f t="shared" ref="G118:G125" si="23">E118*F118</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H118" s="13">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I118" s="13">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J118" s="26"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7613</v>
+        <v>7386</v>
       </c>
       <c r="B119" s="48" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="C119" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D119" s="47">
-        <v>1001061977613</v>
+        <v>1001067017386</v>
       </c>
       <c r="E119" s="22"/>
       <c r="F119" s="21">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G119" s="21">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G119:G126" si="23">E119*F119</f>
         <v>0</v>
       </c>
       <c r="H119" s="13">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I119" s="13">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J119" s="26"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7382</v>
+        <v>7613</v>
       </c>
       <c r="B120" s="48" t="s">
-        <v>85</v>
+        <v>201</v>
       </c>
       <c r="C120" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D120" s="47">
-        <v>1001203117382</v>
+        <v>1001061977613</v>
       </c>
       <c r="E120" s="22"/>
       <c r="F120" s="21">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G120" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H120" s="13">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I120" s="13">
         <v>60</v>
@@ -11826,27 +11825,27 @@
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7616</v>
+        <v>7382</v>
       </c>
       <c r="B121" s="48" t="s">
-        <v>198</v>
+        <v>85</v>
       </c>
       <c r="C121" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D121" s="47">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E121" s="22"/>
       <c r="F121" s="21">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G121" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H121" s="13">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I121" s="13">
         <v>60</v>
@@ -11856,27 +11855,27 @@
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6221</v>
+        <v>7616</v>
       </c>
       <c r="B122" s="48" t="s">
-        <v>87</v>
+        <v>198</v>
       </c>
       <c r="C122" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D122" s="47">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E122" s="22"/>
       <c r="F122" s="21">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G122" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H122" s="13">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I122" s="13">
         <v>60</v>
@@ -11886,16 +11885,16 @@
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="B123" s="48" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C123" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D123" s="47">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E123" s="22"/>
       <c r="F123" s="21">
@@ -11916,192 +11915,192 @@
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>5679</v>
+        <v>6222</v>
       </c>
       <c r="B124" s="48" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C124" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D124" s="47">
-        <v>1001190765679</v>
+        <v>1001205386222</v>
       </c>
       <c r="E124" s="22"/>
       <c r="F124" s="21">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G124" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H124" s="13">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I124" s="13">
         <v>60</v>
       </c>
       <c r="J124" s="26"/>
     </row>
-    <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="100" t="str">
         <f t="shared" si="17"/>
-        <v>7626</v>
+        <v>5679</v>
       </c>
       <c r="B125" s="48" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="C125" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D125" s="47">
-        <v>1001066607626</v>
+        <v>1001190765679</v>
       </c>
       <c r="E125" s="22"/>
       <c r="F125" s="21">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G125" s="21">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H125" s="13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I125" s="13">
         <v>60</v>
       </c>
       <c r="J125" s="26"/>
     </row>
-    <row r="126" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="44" t="s">
+    <row r="126" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="100" t="str">
+        <f t="shared" si="17"/>
+        <v>7626</v>
+      </c>
+      <c r="B126" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="C126" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="47">
+        <v>1001066607626</v>
+      </c>
+      <c r="E126" s="22"/>
+      <c r="F126" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="G126" s="21">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="H126" s="13">
+        <v>1</v>
+      </c>
+      <c r="I126" s="13">
+        <v>60</v>
+      </c>
+      <c r="J126" s="26"/>
+    </row>
+    <row r="127" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="B126" s="39" t="s">
+      <c r="B127" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="C126" s="39"/>
-      <c r="D126" s="39"/>
-      <c r="E126" s="39"/>
-      <c r="F126" s="38"/>
-      <c r="G126" s="39"/>
-      <c r="H126" s="39"/>
-      <c r="I126" s="39"/>
-      <c r="J126" s="40"/>
-    </row>
-    <row r="127" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="100" t="str">
-        <f t="shared" ref="A127:A138" si="24">RIGHT(D127,4)</f>
+      <c r="C127" s="39"/>
+      <c r="D127" s="39"/>
+      <c r="E127" s="39"/>
+      <c r="F127" s="38"/>
+      <c r="G127" s="39"/>
+      <c r="H127" s="39"/>
+      <c r="I127" s="39"/>
+      <c r="J127" s="40"/>
+    </row>
+    <row r="128" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="100" t="str">
+        <f t="shared" ref="A128:A139" si="24">RIGHT(D128,4)</f>
         <v>4584</v>
       </c>
-      <c r="B127" s="92" t="s">
+      <c r="B128" s="92" t="s">
         <v>125</v>
       </c>
-      <c r="C127" s="46" t="s">
+      <c r="C128" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D127" s="107">
+      <c r="D128" s="107">
         <v>1001092674584</v>
       </c>
-      <c r="E127" s="22"/>
-      <c r="F127" s="21">
+      <c r="E128" s="22"/>
+      <c r="F128" s="21">
         <v>2.5</v>
       </c>
-      <c r="G127" s="21">
-        <f>E127</f>
+      <c r="G128" s="21">
+        <f>E128</f>
         <v>0</v>
       </c>
-      <c r="H127" s="13">
+      <c r="H128" s="13">
         <v>7.5</v>
       </c>
-      <c r="I127" s="13">
+      <c r="I128" s="13">
         <v>60</v>
       </c>
-      <c r="J127" s="26"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="100" t="str">
-        <f t="shared" si="24"/>
-        <v>7725</v>
-      </c>
-      <c r="B128" s="92" t="s">
-        <v>218</v>
-      </c>
-      <c r="C128" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="D128" s="47">
-        <v>1001092437725</v>
-      </c>
-      <c r="E128" s="22"/>
-      <c r="F128" s="102">
-        <v>0.3</v>
-      </c>
-      <c r="G128" s="21">
-        <f>E128*F128</f>
-        <v>0</v>
-      </c>
-      <c r="H128" s="26"/>
-      <c r="I128" s="26"/>
-      <c r="J128" s="26" t="str">
-        <f>VLOOKUP(D128,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 6495</v>
-      </c>
+      <c r="J128" s="26"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>5452</v>
-      </c>
-      <c r="B129" s="108" t="s">
-        <v>95</v>
+        <v>7725</v>
+      </c>
+      <c r="B129" s="92" t="s">
+        <v>218</v>
       </c>
       <c r="C129" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D129" s="47">
-        <v>1001092485452</v>
+        <v>1001092437725</v>
       </c>
       <c r="E129" s="22"/>
       <c r="F129" s="102">
-        <v>1.35</v>
+        <v>0.3</v>
       </c>
       <c r="G129" s="21">
-        <f t="shared" ref="G129" si="25">E129</f>
+        <f>E129*F129</f>
         <v>0</v>
       </c>
-      <c r="H129" s="26">
-        <v>4.05</v>
-      </c>
-      <c r="I129" s="26">
-        <v>60</v>
-      </c>
-      <c r="J129" s="26"/>
+      <c r="H129" s="26"/>
+      <c r="I129" s="26"/>
+      <c r="J129" s="26" t="str">
+        <f>VLOOKUP(D129,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 6495</v>
+      </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>3215</v>
+        <v>5452</v>
       </c>
       <c r="B130" s="108" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C130" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D130" s="47">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E130" s="22"/>
       <c r="F130" s="102">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G130" s="21">
-        <f>E130*F130</f>
+        <f t="shared" ref="G130" si="25">E130</f>
         <v>0</v>
       </c>
       <c r="H130" s="26">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I130" s="26">
         <v>60</v>
@@ -12111,27 +12110,27 @@
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>6866</v>
+        <v>3215</v>
       </c>
       <c r="B131" s="108" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C131" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D131" s="47">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E131" s="22"/>
       <c r="F131" s="102">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G131" s="21">
-        <f>E131</f>
+        <f>E131*F131</f>
         <v>0</v>
       </c>
       <c r="H131" s="26">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I131" s="26">
         <v>60</v>
@@ -12141,27 +12140,27 @@
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>5495</v>
-      </c>
-      <c r="B132" s="48" t="s">
-        <v>96</v>
+        <v>6866</v>
+      </c>
+      <c r="B132" s="108" t="s">
+        <v>93</v>
       </c>
       <c r="C132" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="D132" s="101">
-        <v>1001093345495</v>
+        <v>23</v>
+      </c>
+      <c r="D132" s="47">
+        <v>1001095716866</v>
       </c>
       <c r="E132" s="22"/>
       <c r="F132" s="102">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G132" s="21">
-        <f t="shared" ref="G132:G133" si="26">E132*F132</f>
+        <f>E132</f>
         <v>0</v>
       </c>
       <c r="H132" s="26">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I132" s="26">
         <v>60</v>
@@ -12171,158 +12170,159 @@
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7377</v>
+        <v>5495</v>
       </c>
       <c r="B133" s="48" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C133" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D133" s="101">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E133" s="22"/>
       <c r="F133" s="102">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G133" s="21">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G133:G134" si="26">E133*F133</f>
         <v>0</v>
       </c>
       <c r="H133" s="26">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I133" s="26">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J133" s="26"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>6025</v>
+        <v>7377</v>
       </c>
       <c r="B134" s="48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C134" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134" s="101">
-        <v>1001094966025</v>
+        <v>1001095027377</v>
       </c>
       <c r="E134" s="22"/>
       <c r="F134" s="102">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="G134" s="21">
-        <f>E134</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H134" s="26">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="I134" s="26">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J134" s="26"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>6929</v>
+        <v>6025</v>
       </c>
       <c r="B135" s="48" t="s">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="C135" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D135" s="101">
-        <v>1001085476929</v>
+        <v>1001094966025</v>
       </c>
       <c r="E135" s="22"/>
-      <c r="F135" s="102"/>
+      <c r="F135" s="102">
+        <v>3</v>
+      </c>
       <c r="G135" s="21">
         <f>E135</f>
         <v>0</v>
       </c>
-      <c r="H135" s="26"/>
-      <c r="I135" s="26"/>
-      <c r="J135" s="26" t="str">
-        <f>VLOOKUP(D135,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H135" s="26">
+        <v>6</v>
+      </c>
+      <c r="I135" s="26">
+        <v>60</v>
+      </c>
+      <c r="J135" s="26"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7485</v>
+        <v>6929</v>
       </c>
       <c r="B136" s="48" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C136" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D136" s="101">
-        <v>1001107397485</v>
+        <v>1001085476929</v>
       </c>
       <c r="E136" s="22"/>
-      <c r="F136" s="102">
-        <v>0.15</v>
-      </c>
+      <c r="F136" s="102"/>
       <c r="G136" s="21">
-        <f>F136*E136</f>
+        <f>E136</f>
         <v>0</v>
       </c>
       <c r="H136" s="26"/>
       <c r="I136" s="26"/>
-      <c r="J136" s="26"/>
+      <c r="J136" s="26" t="str">
+        <f>VLOOKUP(D136,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7730</v>
+        <v>7485</v>
       </c>
       <c r="B137" s="48" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C137" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D137" s="101">
-        <v>1001097747730</v>
+        <v>1001107397485</v>
       </c>
       <c r="E137" s="22"/>
       <c r="F137" s="102">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="21">
-        <f>E137*F137</f>
+        <f>F137*E137</f>
         <v>0</v>
       </c>
       <c r="H137" s="26"/>
       <c r="I137" s="26"/>
-      <c r="J137" s="26" t="str">
-        <f>VLOOKUP(D137,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 7647</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J137" s="26"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="100" t="str">
         <f t="shared" si="24"/>
-        <v>7731</v>
+        <v>7730</v>
       </c>
       <c r="B138" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C138" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D138" s="101">
-        <v>1001097767731</v>
+        <v>1001097747730</v>
       </c>
       <c r="E138" s="22"/>
       <c r="F138" s="102">
@@ -12332,83 +12332,82 @@
         <f>E138*F138</f>
         <v>0</v>
       </c>
-      <c r="H138" s="26">
-        <v>1</v>
-      </c>
-      <c r="I138" s="26">
-        <v>30</v>
-      </c>
+      <c r="H138" s="26"/>
+      <c r="I138" s="26"/>
       <c r="J138" s="26" t="str">
         <f>VLOOKUP(D138,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 7647</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="100" t="str">
+        <f t="shared" si="24"/>
+        <v>7731</v>
+      </c>
+      <c r="B139" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="C139" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" s="101">
+        <v>1001097767731</v>
+      </c>
+      <c r="E139" s="22"/>
+      <c r="F139" s="102">
+        <v>0.1</v>
+      </c>
+      <c r="G139" s="21">
+        <f>E139*F139</f>
+        <v>0</v>
+      </c>
+      <c r="H139" s="26">
+        <v>1</v>
+      </c>
+      <c r="I139" s="26">
+        <v>30</v>
+      </c>
+      <c r="J139" s="26" t="str">
+        <f>VLOOKUP(D139,[1]Бланк!$D:$J,7,0)</f>
         <v>Ротация кода 7651</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="44" t="s">
+    <row r="140" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="B139" s="39" t="s">
+      <c r="B140" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="C139" s="39"/>
-      <c r="D139" s="39"/>
-      <c r="E139" s="39"/>
-      <c r="F139" s="38"/>
-      <c r="G139" s="39"/>
-      <c r="H139" s="39"/>
-      <c r="I139" s="39"/>
-      <c r="J139" s="40"/>
-    </row>
-    <row r="140" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="100" t="str">
-        <f t="shared" ref="A140:A152" si="27">RIGHT(D140,4)</f>
+      <c r="C140" s="39"/>
+      <c r="D140" s="39"/>
+      <c r="E140" s="39"/>
+      <c r="F140" s="38"/>
+      <c r="G140" s="39"/>
+      <c r="H140" s="39"/>
+      <c r="I140" s="39"/>
+      <c r="J140" s="40"/>
+    </row>
+    <row r="141" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="100" t="str">
+        <f t="shared" ref="A141:A153" si="27">RIGHT(D141,4)</f>
         <v>7090</v>
       </c>
-      <c r="B140" s="32" t="s">
+      <c r="B141" s="32" t="s">
         <v>102</v>
-      </c>
-      <c r="C140" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="D140" s="47">
-        <v>1001084217090</v>
-      </c>
-      <c r="E140" s="22"/>
-      <c r="F140" s="21">
-        <v>0.3</v>
-      </c>
-      <c r="G140" s="21">
-        <f t="shared" ref="G140:G141" si="28">E140*F140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="13">
-        <v>1.8</v>
-      </c>
-      <c r="I140" s="13">
-        <v>50</v>
-      </c>
-      <c r="J140" s="26"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="100" t="str">
-        <f t="shared" si="27"/>
-        <v>7187</v>
-      </c>
-      <c r="B141" s="32" t="s">
-        <v>103</v>
       </c>
       <c r="C141" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D141" s="47">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E141" s="22"/>
       <c r="F141" s="21">
         <v>0.3</v>
       </c>
       <c r="G141" s="21">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G141:G142" si="28">E141*F141</f>
         <v>0</v>
       </c>
       <c r="H141" s="13">
@@ -12422,117 +12421,117 @@
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6008</v>
+        <v>7187</v>
       </c>
       <c r="B142" s="32" t="s">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="C142" s="46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D142" s="47">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E142" s="22"/>
       <c r="F142" s="21">
         <v>0.3</v>
       </c>
       <c r="G142" s="21">
-        <f>E142</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H142" s="13">
         <v>1.8</v>
       </c>
       <c r="I142" s="13">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J142" s="26"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6620</v>
+        <v>6008</v>
       </c>
       <c r="B143" s="32" t="s">
-        <v>99</v>
+        <v>196</v>
       </c>
       <c r="C143" s="46" t="s">
         <v>23</v>
       </c>
       <c r="D143" s="47">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E143" s="22"/>
       <c r="F143" s="21">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G143" s="21">
         <f>E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="13">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I143" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J143" s="26"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7103</v>
+        <v>6620</v>
       </c>
       <c r="B144" s="32" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C144" s="46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D144" s="47">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E144" s="22"/>
       <c r="F144" s="21">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G144" s="21">
-        <f t="shared" ref="G144:G151" si="29">E144*F144</f>
+        <f>E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="13">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I144" s="13">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J144" s="26"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7092</v>
+        <v>7103</v>
       </c>
       <c r="B145" s="32" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C145" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D145" s="47">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E145" s="22"/>
       <c r="F145" s="21">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G145" s="21">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G145:G152" si="29">E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="13">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I145" s="13">
         <v>50</v>
@@ -12542,57 +12541,57 @@
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6228</v>
+        <v>7092</v>
       </c>
       <c r="B146" s="32" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C146" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D146" s="47">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E146" s="22"/>
       <c r="F146" s="21">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G146" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H146" s="13">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I146" s="13">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J146" s="26"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6208</v>
+        <v>6228</v>
       </c>
       <c r="B147" s="32" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C147" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D147" s="47">
-        <v>1001220226208</v>
+        <v>1001225416228</v>
       </c>
       <c r="E147" s="22"/>
       <c r="F147" s="21">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G147" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H147" s="13">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I147" s="13">
         <v>45</v>
@@ -12602,142 +12601,143 @@
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6754</v>
+        <v>6208</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="C148" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D148" s="47">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E148" s="22"/>
       <c r="F148" s="21">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G148" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H148" s="13">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I148" s="13">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J148" s="26"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>6279</v>
+        <v>6754</v>
       </c>
       <c r="B149" s="32" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C149" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D149" s="47">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E149" s="22"/>
       <c r="F149" s="21">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G149" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H149" s="13">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I149" s="13">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J149" s="26"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7612</v>
+        <v>6279</v>
       </c>
       <c r="B150" s="32" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C150" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D150" s="47">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E150" s="22"/>
       <c r="F150" s="21">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G150" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H150" s="13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I150" s="13">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J150" s="26"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7344</v>
+        <v>7612</v>
       </c>
       <c r="B151" s="32" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="C151" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D151" s="47">
-        <v>1001122287344</v>
+        <v>1001453907612</v>
       </c>
       <c r="E151" s="22"/>
       <c r="F151" s="21">
-        <v>0.33800000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="G151" s="21">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H151" s="13"/>
-      <c r="I151" s="13"/>
-      <c r="J151" s="26" t="str">
-        <f>VLOOKUP(D151,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H151" s="13">
+        <v>1</v>
+      </c>
+      <c r="I151" s="13">
+        <v>60</v>
+      </c>
+      <c r="J151" s="26"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="100" t="str">
         <f t="shared" si="27"/>
-        <v>7345</v>
+        <v>7344</v>
       </c>
       <c r="B152" s="32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C152" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D152" s="47">
-        <v>1001123677345</v>
+        <v>1001122287344</v>
       </c>
       <c r="E152" s="22"/>
       <c r="F152" s="21">
-        <v>0.32500000000000001</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="G152" s="21">
-        <f>E152*F152</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H152" s="13"/>
@@ -12747,37 +12747,56 @@
         <v>Новинка</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="45"/>
-      <c r="B153" s="42" t="s">
+    <row r="153" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="100" t="str">
+        <f t="shared" si="27"/>
+        <v>7345</v>
+      </c>
+      <c r="B153" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C153" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D153" s="47">
+        <v>1001123677345</v>
+      </c>
+      <c r="E153" s="22"/>
+      <c r="F153" s="21">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G153" s="21">
+        <f>E153*F153</f>
+        <v>0</v>
+      </c>
+      <c r="H153" s="13"/>
+      <c r="I153" s="13"/>
+      <c r="J153" s="26" t="str">
+        <f>VLOOKUP(D153,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="45"/>
+      <c r="B154" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="C153" s="14"/>
-      <c r="D153" s="33"/>
-      <c r="E153" s="15">
-        <f>SUM(E10:E150)</f>
+      <c r="C154" s="14"/>
+      <c r="D154" s="33"/>
+      <c r="E154" s="15">
+        <f>SUM(E10:E151)</f>
         <v>0</v>
       </c>
-      <c r="F153" s="15"/>
-      <c r="G153" s="15">
-        <f>SUM(G11:G152)</f>
+      <c r="F154" s="15"/>
+      <c r="G154" s="15">
+        <f>SUM(G11:G153)</f>
         <v>0</v>
       </c>
-      <c r="H153" s="15"/>
-      <c r="I153" s="15"/>
-      <c r="J153" s="15"/>
-    </row>
-    <row r="154" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="34"/>
-      <c r="C154" s="16"/>
-      <c r="D154" s="37"/>
-      <c r="F154" s="17"/>
-      <c r="G154" s="17"/>
-      <c r="H154" s="18"/>
-      <c r="I154" s="18"/>
-      <c r="J154" s="19"/>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H154" s="15"/>
+      <c r="I154" s="15"/>
+      <c r="J154" s="15"/>
+    </row>
+    <row r="155" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B155" s="34"/>
       <c r="C155" s="16"/>
       <c r="D155" s="37"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ Новое Время_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4315AA7-7C00-4BCE-A27A-2EA65C6EA1BD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740C0D1B-4E2A-45FB-99D7-512A38AEC01C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$154</definedName>
     <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$414</definedName>
     <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$414</definedName>
   </definedNames>
@@ -491,7 +492,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="225">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1164,6 +1165,9 @@
   </si>
   <si>
     <t>САЛЯМИ ZHAZIRA ASLAM в/к в/у 0.82кг</t>
+  </si>
+  <si>
+    <t>РУБЛЕНЫЕ сос ц/о в/у 0.36кг 8шт.</t>
   </si>
 </sst>
 </file>
@@ -9758,16 +9762,16 @@
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="100" t="str">
         <f t="shared" si="1"/>
-        <v>6765</v>
+        <v>7520</v>
       </c>
       <c r="B50" s="48" t="s">
-        <v>41</v>
+        <v>224</v>
       </c>
       <c r="C50" s="46" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="47">
-        <v>1001023696765</v>
+        <v>1001023697520</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="102">
@@ -9777,12 +9781,8 @@
         <f>E50*F50</f>
         <v>0</v>
       </c>
-      <c r="H50" s="26">
-        <v>2.16</v>
-      </c>
-      <c r="I50" s="26">
-        <v>45</v>
-      </c>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
       <c r="J50" s="26"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -26277,6 +26277,7 @@
       <c r="J1502" s="19"/>
     </row>
   </sheetData>
+  <autoFilter ref="A9:J154" xr:uid="{65740D68-3846-46B5-894A-AD92E783A223}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
